--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1197,3505 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124841283</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>609215</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7017959</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124839286</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>658</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>609042</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7018085</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124839525</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91673</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>898</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>609068</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7018108</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124841439</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>609243</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7017992</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124836828</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>112</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>609243</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7018223</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124841120</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>609178</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7017968</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124836321</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>609324</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7018195</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124836317</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>658</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>609320</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7018199</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124837151</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>609253</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7018298</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124837340</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>609241</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7018298</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124836351</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91361</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>609330</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7018199</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124836744</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>609243</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7018254</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124840385</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>609100</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7018053</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124836692</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>609259</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7018252</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124837159</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>609248</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7018303</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124836147</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>609334</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7018163</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124836811</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91361</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>609241</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7018250</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124835873</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91673</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>898</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>609372</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7018137</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124838979</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>658</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>609132</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7018018</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124840461</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>658</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>609114</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7018022</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124837429</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>658</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>609251</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7018311</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124835707</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91413</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>609360</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7018137</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124838762</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>609202</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7018017</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124839307</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>658</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>609077</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7018074</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124836709</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>658</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>609251</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7018241</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124838903</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>609168</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7018021</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124839318</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>609091</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7018078</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124837331</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91361</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>609236</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7018288</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124835668</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>658</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>609359</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7018158</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124835740</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>609356</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7018141</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124837411</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>609251</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7018311</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124837223</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91026</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>609229</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7018310</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124838913</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>609144</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7018039</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124841153</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>658</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>609180</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7017969</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -2537,10 +2537,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124836692</v>
+        <v>124836147</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2549,25 +2549,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609259</v>
+        <v>609334</v>
       </c>
       <c r="R19" t="n">
-        <v>7018252</v>
+        <v>7018163</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124837159</v>
+        <v>124836692</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,25 +2651,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609248</v>
+        <v>609259</v>
       </c>
       <c r="R20" t="n">
-        <v>7018303</v>
+        <v>7018252</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124836147</v>
+        <v>124837159</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609334</v>
+        <v>609248</v>
       </c>
       <c r="R21" t="n">
-        <v>7018163</v>
+        <v>7018303</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124836811</v>
+        <v>124835873</v>
       </c>
       <c r="B22" t="n">
-        <v>91361</v>
+        <v>91673</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>898</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609241</v>
+        <v>609372</v>
       </c>
       <c r="R22" t="n">
-        <v>7018250</v>
+        <v>7018137</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2945,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124835873</v>
+        <v>124836811</v>
       </c>
       <c r="B23" t="n">
-        <v>91673</v>
+        <v>91361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,21 +2961,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609372</v>
+        <v>609241</v>
       </c>
       <c r="R23" t="n">
-        <v>7018137</v>
+        <v>7018250</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124841283</v>
+        <v>124837151</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,42 +1211,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609215</v>
+        <v>609253</v>
       </c>
       <c r="R6" t="n">
-        <v>7017959</v>
+        <v>7018298</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1305,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124839286</v>
+        <v>124836744</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,21 +1317,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1345,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609042</v>
+        <v>609243</v>
       </c>
       <c r="R7" t="n">
-        <v>7018085</v>
+        <v>7018254</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1407,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124839525</v>
+        <v>124841120</v>
       </c>
       <c r="B8" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,25 +1415,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1447,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609068</v>
+        <v>609178</v>
       </c>
       <c r="R8" t="n">
-        <v>7018108</v>
+        <v>7017968</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1509,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124841439</v>
+        <v>124837429</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,42 +1517,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609243</v>
+        <v>609251</v>
       </c>
       <c r="R9" t="n">
-        <v>7017992</v>
+        <v>7018311</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1615,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124836828</v>
+        <v>124839525</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>91673</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,25 +1619,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609243</v>
+        <v>609068</v>
       </c>
       <c r="R10" t="n">
-        <v>7018223</v>
+        <v>7018108</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1717,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124841120</v>
+        <v>124836147</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1757,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609178</v>
+        <v>609334</v>
       </c>
       <c r="R11" t="n">
-        <v>7017968</v>
+        <v>7018163</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1819,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124836321</v>
+        <v>124837411</v>
       </c>
       <c r="B12" t="n">
         <v>91012</v>
@@ -1859,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609324</v>
+        <v>609251</v>
       </c>
       <c r="R12" t="n">
-        <v>7018195</v>
+        <v>7018311</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1921,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836317</v>
+        <v>124838903</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609320</v>
+        <v>609168</v>
       </c>
       <c r="R13" t="n">
-        <v>7018199</v>
+        <v>7018021</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2023,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124837151</v>
+        <v>124836828</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2031,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609253</v>
+        <v>609243</v>
       </c>
       <c r="R14" t="n">
-        <v>7018298</v>
+        <v>7018223</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2125,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124837340</v>
+        <v>124835740</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,25 +2129,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609241</v>
+        <v>609356</v>
       </c>
       <c r="R15" t="n">
-        <v>7018298</v>
+        <v>7018141</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2227,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124836351</v>
+        <v>124839318</v>
       </c>
       <c r="B16" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,25 +2231,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609330</v>
+        <v>609091</v>
       </c>
       <c r="R16" t="n">
-        <v>7018199</v>
+        <v>7018078</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2329,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124836744</v>
+        <v>124835873</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,25 +2333,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2369,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609243</v>
+        <v>609372</v>
       </c>
       <c r="R17" t="n">
-        <v>7018254</v>
+        <v>7018137</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2431,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124840385</v>
+        <v>124839286</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2443,42 +2435,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609100</v>
+        <v>609042</v>
       </c>
       <c r="R18" t="n">
-        <v>7018053</v>
+        <v>7018085</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2537,7 +2525,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124836147</v>
+        <v>124838979</v>
       </c>
       <c r="B19" t="n">
         <v>91299</v>
@@ -2577,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609334</v>
+        <v>609132</v>
       </c>
       <c r="R19" t="n">
-        <v>7018163</v>
+        <v>7018018</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2639,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124836692</v>
+        <v>124836351</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>91361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,25 +2639,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2679,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609259</v>
+        <v>609330</v>
       </c>
       <c r="R20" t="n">
-        <v>7018252</v>
+        <v>7018199</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2741,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124837159</v>
+        <v>124836692</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2753,25 +2741,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2781,10 +2769,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609248</v>
+        <v>609259</v>
       </c>
       <c r="R21" t="n">
-        <v>7018303</v>
+        <v>7018252</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2843,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124835873</v>
+        <v>124840385</v>
       </c>
       <c r="B22" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,34 +2847,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609372</v>
+        <v>609100</v>
       </c>
       <c r="R22" t="n">
-        <v>7018137</v>
+        <v>7018053</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2945,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124836811</v>
+        <v>124841439</v>
       </c>
       <c r="B23" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2961,34 +2953,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609241</v>
+        <v>609243</v>
       </c>
       <c r="R23" t="n">
-        <v>7018250</v>
+        <v>7017992</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3047,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838979</v>
+        <v>124841283</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,38 +3055,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609132</v>
+        <v>609215</v>
       </c>
       <c r="R24" t="n">
-        <v>7018018</v>
+        <v>7017959</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3149,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124840461</v>
+        <v>124841153</v>
       </c>
       <c r="B25" t="n">
         <v>91299</v>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609114</v>
+        <v>609180</v>
       </c>
       <c r="R25" t="n">
-        <v>7018022</v>
+        <v>7017969</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124837429</v>
+        <v>124838762</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,38 +3263,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609251</v>
+        <v>609202</v>
       </c>
       <c r="R26" t="n">
-        <v>7018311</v>
+        <v>7018017</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3353,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124835707</v>
+        <v>124840461</v>
       </c>
       <c r="B27" t="n">
-        <v>91413</v>
+        <v>91299</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,25 +3369,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3393,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609360</v>
+        <v>609114</v>
       </c>
       <c r="R27" t="n">
-        <v>7018137</v>
+        <v>7018022</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3439,21 +3443,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3470,10 +3459,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838762</v>
+        <v>124836321</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3482,42 +3471,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609202</v>
+        <v>609324</v>
       </c>
       <c r="R28" t="n">
-        <v>7018017</v>
+        <v>7018195</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3576,10 +3561,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124839307</v>
+        <v>124837331</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3588,25 +3573,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3616,10 +3601,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609077</v>
+        <v>609236</v>
       </c>
       <c r="R29" t="n">
-        <v>7018074</v>
+        <v>7018288</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3678,7 +3663,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124836709</v>
+        <v>124838913</v>
       </c>
       <c r="B30" t="n">
         <v>91299</v>
@@ -3718,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609251</v>
+        <v>609144</v>
       </c>
       <c r="R30" t="n">
-        <v>7018241</v>
+        <v>7018039</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3780,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124838903</v>
+        <v>124839307</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3796,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3820,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609168</v>
+        <v>609077</v>
       </c>
       <c r="R31" t="n">
-        <v>7018021</v>
+        <v>7018074</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3882,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124839318</v>
+        <v>124836709</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3898,21 +3883,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3922,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609091</v>
+        <v>609251</v>
       </c>
       <c r="R32" t="n">
-        <v>7018078</v>
+        <v>7018241</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3984,7 +3969,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124837331</v>
+        <v>124836811</v>
       </c>
       <c r="B33" t="n">
         <v>91361</v>
@@ -4024,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609236</v>
+        <v>609241</v>
       </c>
       <c r="R33" t="n">
-        <v>7018288</v>
+        <v>7018250</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4188,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124835740</v>
+        <v>124837340</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4200,25 +4185,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4213,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609356</v>
+        <v>609241</v>
       </c>
       <c r="R35" t="n">
-        <v>7018141</v>
+        <v>7018298</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4290,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124837411</v>
+        <v>124835707</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>91413</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4302,25 +4287,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609251</v>
+        <v>609360</v>
       </c>
       <c r="R36" t="n">
-        <v>7018311</v>
+        <v>7018137</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4376,6 +4361,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4392,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124837223</v>
+        <v>124836317</v>
       </c>
       <c r="B37" t="n">
-        <v>91026</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4408,21 +4408,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609229</v>
+        <v>609320</v>
       </c>
       <c r="R37" t="n">
-        <v>7018310</v>
+        <v>7018199</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124838913</v>
+        <v>124837159</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609144</v>
+        <v>609248</v>
       </c>
       <c r="R38" t="n">
-        <v>7018039</v>
+        <v>7018303</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124841153</v>
+        <v>124837223</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4612,21 +4612,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609180</v>
+        <v>609229</v>
       </c>
       <c r="R39" t="n">
-        <v>7017969</v>
+        <v>7018310</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124837151</v>
+        <v>124837429</v>
       </c>
       <c r="B6" t="n">
         <v>91299</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609253</v>
+        <v>609251</v>
       </c>
       <c r="R6" t="n">
-        <v>7018298</v>
+        <v>7018311</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124836744</v>
+        <v>124841153</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609243</v>
+        <v>609180</v>
       </c>
       <c r="R7" t="n">
-        <v>7018254</v>
+        <v>7017969</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124841120</v>
+        <v>124839307</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609178</v>
+        <v>609077</v>
       </c>
       <c r="R8" t="n">
-        <v>7017968</v>
+        <v>7018074</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124837429</v>
+        <v>124837223</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609251</v>
+        <v>609229</v>
       </c>
       <c r="R9" t="n">
-        <v>7018311</v>
+        <v>7018310</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124839525</v>
+        <v>124835873</v>
       </c>
       <c r="B10" t="n">
         <v>91673</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609068</v>
+        <v>609372</v>
       </c>
       <c r="R10" t="n">
-        <v>7018108</v>
+        <v>7018137</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124836147</v>
+        <v>124836709</v>
       </c>
       <c r="B11" t="n">
         <v>91299</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609334</v>
+        <v>609251</v>
       </c>
       <c r="R11" t="n">
-        <v>7018163</v>
+        <v>7018241</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124837411</v>
+        <v>124836317</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609251</v>
+        <v>609320</v>
       </c>
       <c r="R12" t="n">
-        <v>7018311</v>
+        <v>7018199</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124838903</v>
+        <v>124836321</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609168</v>
+        <v>609324</v>
       </c>
       <c r="R13" t="n">
-        <v>7018021</v>
+        <v>7018195</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124836828</v>
+        <v>124837411</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,21 +2031,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609243</v>
+        <v>609251</v>
       </c>
       <c r="R14" t="n">
-        <v>7018223</v>
+        <v>7018311</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124835740</v>
+        <v>124836147</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609356</v>
+        <v>609334</v>
       </c>
       <c r="R15" t="n">
-        <v>7018141</v>
+        <v>7018163</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124839318</v>
+        <v>124835740</v>
       </c>
       <c r="B16" t="n">
         <v>91012</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609091</v>
+        <v>609356</v>
       </c>
       <c r="R16" t="n">
-        <v>7018078</v>
+        <v>7018141</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124835873</v>
+        <v>124835707</v>
       </c>
       <c r="B17" t="n">
-        <v>91673</v>
+        <v>91413</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,25 +2333,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>898</v>
+        <v>4217</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609372</v>
+        <v>609360</v>
       </c>
       <c r="R17" t="n">
         <v>7018137</v>
@@ -2407,6 +2407,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2525,10 +2540,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124838979</v>
+        <v>124837331</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,25 +2552,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,10 +2580,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609132</v>
+        <v>609236</v>
       </c>
       <c r="R19" t="n">
-        <v>7018018</v>
+        <v>7018288</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2627,10 +2642,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124836351</v>
+        <v>124837151</v>
       </c>
       <c r="B20" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,25 +2654,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2667,10 +2682,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609330</v>
+        <v>609253</v>
       </c>
       <c r="R20" t="n">
-        <v>7018199</v>
+        <v>7018298</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2729,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124836692</v>
+        <v>124838979</v>
       </c>
       <c r="B21" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,25 +2756,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2769,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609259</v>
+        <v>609132</v>
       </c>
       <c r="R21" t="n">
-        <v>7018252</v>
+        <v>7018018</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2831,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124840385</v>
+        <v>124839318</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,42 +2858,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609100</v>
+        <v>609091</v>
       </c>
       <c r="R22" t="n">
-        <v>7018053</v>
+        <v>7018078</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2937,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124841439</v>
+        <v>124836828</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>90962</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,32 +2960,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
@@ -2984,7 +2991,7 @@
         <v>609243</v>
       </c>
       <c r="R23" t="n">
-        <v>7017992</v>
+        <v>7018223</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3043,10 +3050,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124841283</v>
+        <v>124835668</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,42 +3062,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609215</v>
+        <v>609359</v>
       </c>
       <c r="R24" t="n">
-        <v>7017959</v>
+        <v>7018158</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3149,10 +3152,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124841153</v>
+        <v>124837340</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,25 +3164,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609180</v>
+        <v>609241</v>
       </c>
       <c r="R25" t="n">
-        <v>7017969</v>
+        <v>7018298</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3251,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838762</v>
+        <v>124836692</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,42 +3266,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609202</v>
+        <v>609259</v>
       </c>
       <c r="R26" t="n">
-        <v>7018017</v>
+        <v>7018252</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3357,10 +3356,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124840461</v>
+        <v>124837159</v>
       </c>
       <c r="B27" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3373,21 +3372,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609114</v>
+        <v>609248</v>
       </c>
       <c r="R27" t="n">
-        <v>7018022</v>
+        <v>7018303</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3459,10 +3458,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124836321</v>
+        <v>124836811</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,25 +3470,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3499,10 +3498,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609324</v>
+        <v>609241</v>
       </c>
       <c r="R28" t="n">
-        <v>7018195</v>
+        <v>7018250</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3561,10 +3560,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124837331</v>
+        <v>124840385</v>
       </c>
       <c r="B29" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3577,34 +3576,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609236</v>
+        <v>609100</v>
       </c>
       <c r="R29" t="n">
-        <v>7018288</v>
+        <v>7018053</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3663,7 +3666,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838913</v>
+        <v>124840461</v>
       </c>
       <c r="B30" t="n">
         <v>91299</v>
@@ -3703,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609144</v>
+        <v>609114</v>
       </c>
       <c r="R30" t="n">
-        <v>7018039</v>
+        <v>7018022</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3765,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124839307</v>
+        <v>124841439</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3777,38 +3780,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609077</v>
+        <v>609243</v>
       </c>
       <c r="R31" t="n">
-        <v>7018074</v>
+        <v>7017992</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3867,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124836709</v>
+        <v>124838903</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3883,21 +3890,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609251</v>
+        <v>609168</v>
       </c>
       <c r="R32" t="n">
-        <v>7018241</v>
+        <v>7018021</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3969,10 +3976,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124836811</v>
+        <v>124841120</v>
       </c>
       <c r="B33" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3981,25 +3988,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609241</v>
+        <v>609178</v>
       </c>
       <c r="R33" t="n">
-        <v>7018250</v>
+        <v>7017968</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4071,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124835668</v>
+        <v>124836744</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4087,21 +4094,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4111,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609359</v>
+        <v>609243</v>
       </c>
       <c r="R34" t="n">
-        <v>7018158</v>
+        <v>7018254</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4173,10 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124837340</v>
+        <v>124841283</v>
       </c>
       <c r="B35" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,38 +4192,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609241</v>
+        <v>609215</v>
       </c>
       <c r="R35" t="n">
-        <v>7018298</v>
+        <v>7017959</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4275,10 +4286,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124835707</v>
+        <v>124838762</v>
       </c>
       <c r="B36" t="n">
-        <v>91413</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4287,38 +4298,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609360</v>
+        <v>609202</v>
       </c>
       <c r="R36" t="n">
-        <v>7018137</v>
+        <v>7018017</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4361,21 +4376,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4392,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124836317</v>
+        <v>124839525</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4404,25 +4404,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609320</v>
+        <v>609068</v>
       </c>
       <c r="R37" t="n">
-        <v>7018199</v>
+        <v>7018108</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124837159</v>
+        <v>124838913</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609248</v>
+        <v>609144</v>
       </c>
       <c r="R38" t="n">
-        <v>7018303</v>
+        <v>7018039</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124837223</v>
+        <v>124836351</v>
       </c>
       <c r="B39" t="n">
-        <v>91026</v>
+        <v>91361</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,25 +4608,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609229</v>
+        <v>609330</v>
       </c>
       <c r="R39" t="n">
-        <v>7018310</v>
+        <v>7018199</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124837429</v>
+        <v>124836744</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R6" t="n">
-        <v>7018311</v>
+        <v>7018254</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124841153</v>
+        <v>124835740</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609180</v>
+        <v>609356</v>
       </c>
       <c r="R7" t="n">
-        <v>7017969</v>
+        <v>7018141</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124839307</v>
+        <v>124836321</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609077</v>
+        <v>609324</v>
       </c>
       <c r="R8" t="n">
-        <v>7018074</v>
+        <v>7018195</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124837223</v>
+        <v>124841120</v>
       </c>
       <c r="B9" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609229</v>
+        <v>609178</v>
       </c>
       <c r="R9" t="n">
-        <v>7018310</v>
+        <v>7017968</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124835873</v>
+        <v>124837151</v>
       </c>
       <c r="B10" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,25 +1619,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609372</v>
+        <v>609253</v>
       </c>
       <c r="R10" t="n">
-        <v>7018137</v>
+        <v>7018298</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124836709</v>
+        <v>124839525</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609251</v>
+        <v>609068</v>
       </c>
       <c r="R11" t="n">
-        <v>7018241</v>
+        <v>7018108</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124836317</v>
+        <v>124837411</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609320</v>
+        <v>609251</v>
       </c>
       <c r="R12" t="n">
-        <v>7018199</v>
+        <v>7018311</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836321</v>
+        <v>124836317</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609324</v>
+        <v>609320</v>
       </c>
       <c r="R13" t="n">
-        <v>7018195</v>
+        <v>7018199</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124837411</v>
+        <v>124835873</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,25 +2027,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609251</v>
+        <v>609372</v>
       </c>
       <c r="R14" t="n">
-        <v>7018311</v>
+        <v>7018137</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124836147</v>
+        <v>124839307</v>
       </c>
       <c r="B15" t="n">
         <v>91299</v>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609334</v>
+        <v>609077</v>
       </c>
       <c r="R15" t="n">
-        <v>7018163</v>
+        <v>7018074</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124835740</v>
+        <v>124838979</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609356</v>
+        <v>609132</v>
       </c>
       <c r="R16" t="n">
-        <v>7018141</v>
+        <v>7018018</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124835707</v>
+        <v>124837223</v>
       </c>
       <c r="B17" t="n">
-        <v>91413</v>
+        <v>91026</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,25 +2333,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4217</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609360</v>
+        <v>609229</v>
       </c>
       <c r="R17" t="n">
-        <v>7018137</v>
+        <v>7018310</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2407,21 +2407,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2438,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124839286</v>
+        <v>124836692</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2450,25 +2435,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609042</v>
+        <v>609259</v>
       </c>
       <c r="R18" t="n">
-        <v>7018085</v>
+        <v>7018252</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2540,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124837331</v>
+        <v>124836147</v>
       </c>
       <c r="B19" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2552,25 +2537,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2580,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609236</v>
+        <v>609334</v>
       </c>
       <c r="R19" t="n">
-        <v>7018288</v>
+        <v>7018163</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2642,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124837151</v>
+        <v>124838762</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,38 +2639,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609253</v>
+        <v>609202</v>
       </c>
       <c r="R20" t="n">
-        <v>7018298</v>
+        <v>7018017</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2744,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838979</v>
+        <v>124837340</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2756,25 +2745,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2784,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609132</v>
+        <v>609241</v>
       </c>
       <c r="R21" t="n">
-        <v>7018018</v>
+        <v>7018298</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2846,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124839318</v>
+        <v>124838913</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609091</v>
+        <v>609144</v>
       </c>
       <c r="R22" t="n">
-        <v>7018078</v>
+        <v>7018039</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2948,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124836828</v>
+        <v>124839318</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2988,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609243</v>
+        <v>609091</v>
       </c>
       <c r="R23" t="n">
-        <v>7018223</v>
+        <v>7018078</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3050,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124835668</v>
+        <v>124841283</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3062,38 +3051,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609359</v>
+        <v>609215</v>
       </c>
       <c r="R24" t="n">
-        <v>7018158</v>
+        <v>7017959</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3152,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124837340</v>
+        <v>124837331</v>
       </c>
       <c r="B25" t="n">
-        <v>90977</v>
+        <v>91361</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3164,25 +3157,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3192,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609241</v>
+        <v>609236</v>
       </c>
       <c r="R25" t="n">
-        <v>7018298</v>
+        <v>7018288</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3254,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124836692</v>
+        <v>124838903</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3266,25 +3259,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3294,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609259</v>
+        <v>609168</v>
       </c>
       <c r="R26" t="n">
-        <v>7018252</v>
+        <v>7018021</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3356,10 +3349,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124837159</v>
+        <v>124836351</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3368,25 +3361,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3396,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609248</v>
+        <v>609330</v>
       </c>
       <c r="R27" t="n">
-        <v>7018303</v>
+        <v>7018199</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3458,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124836811</v>
+        <v>124836828</v>
       </c>
       <c r="B28" t="n">
-        <v>91361</v>
+        <v>90962</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3470,25 +3463,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3498,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609241</v>
+        <v>609243</v>
       </c>
       <c r="R28" t="n">
-        <v>7018250</v>
+        <v>7018223</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3560,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124840385</v>
+        <v>124836811</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3576,38 +3569,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609100</v>
+        <v>609241</v>
       </c>
       <c r="R29" t="n">
-        <v>7018053</v>
+        <v>7018250</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3666,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124840461</v>
+        <v>124837429</v>
       </c>
       <c r="B30" t="n">
         <v>91299</v>
@@ -3706,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609114</v>
+        <v>609251</v>
       </c>
       <c r="R30" t="n">
-        <v>7018022</v>
+        <v>7018311</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3768,10 +3757,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124841439</v>
+        <v>124840461</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3780,42 +3769,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609243</v>
+        <v>609114</v>
       </c>
       <c r="R31" t="n">
-        <v>7017992</v>
+        <v>7018022</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3874,10 +3859,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124838903</v>
+        <v>124835707</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91413</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,25 +3871,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609168</v>
+        <v>609360</v>
       </c>
       <c r="R32" t="n">
-        <v>7018021</v>
+        <v>7018137</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3960,6 +3945,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3976,7 +3976,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124841120</v>
+        <v>124837159</v>
       </c>
       <c r="B33" t="n">
         <v>91012</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609178</v>
+        <v>609248</v>
       </c>
       <c r="R33" t="n">
-        <v>7017968</v>
+        <v>7018303</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4078,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124836744</v>
+        <v>124841153</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4094,21 +4094,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609243</v>
+        <v>609180</v>
       </c>
       <c r="R34" t="n">
-        <v>7018254</v>
+        <v>7017969</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4180,10 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124841283</v>
+        <v>124836709</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,42 +4192,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609215</v>
+        <v>609251</v>
       </c>
       <c r="R35" t="n">
-        <v>7017959</v>
+        <v>7018241</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4286,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124838762</v>
+        <v>124839286</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4298,42 +4294,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609202</v>
+        <v>609042</v>
       </c>
       <c r="R36" t="n">
-        <v>7018017</v>
+        <v>7018085</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4392,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124839525</v>
+        <v>124835668</v>
       </c>
       <c r="B37" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4404,25 +4396,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4432,10 +4424,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609068</v>
+        <v>609359</v>
       </c>
       <c r="R37" t="n">
-        <v>7018108</v>
+        <v>7018158</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,10 +4486,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124838913</v>
+        <v>124840385</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,38 +4498,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609144</v>
+        <v>609100</v>
       </c>
       <c r="R38" t="n">
-        <v>7018039</v>
+        <v>7018053</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124836351</v>
+        <v>124841439</v>
       </c>
       <c r="B39" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4612,34 +4608,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609330</v>
+        <v>609243</v>
       </c>
       <c r="R39" t="n">
-        <v>7018199</v>
+        <v>7017992</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124839318</v>
+        <v>124837331</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609091</v>
+        <v>609236</v>
       </c>
       <c r="R23" t="n">
-        <v>7018078</v>
+        <v>7018288</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124841283</v>
+        <v>124839318</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,42 +3051,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609215</v>
+        <v>609091</v>
       </c>
       <c r="R24" t="n">
-        <v>7017959</v>
+        <v>7018078</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3145,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124837331</v>
+        <v>124841283</v>
       </c>
       <c r="B25" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,34 +3157,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609236</v>
+        <v>609215</v>
       </c>
       <c r="R25" t="n">
-        <v>7018288</v>
+        <v>7017959</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3859,10 +3859,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124835707</v>
+        <v>124841153</v>
       </c>
       <c r="B32" t="n">
-        <v>91413</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,25 +3871,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609360</v>
+        <v>609180</v>
       </c>
       <c r="R32" t="n">
-        <v>7018137</v>
+        <v>7017969</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3945,21 +3945,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3976,10 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124837159</v>
+        <v>124835707</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>91413</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,25 +3973,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +4001,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609248</v>
+        <v>609360</v>
       </c>
       <c r="R33" t="n">
-        <v>7018303</v>
+        <v>7018137</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4062,6 +4047,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4078,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124841153</v>
+        <v>124837159</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4094,21 +4094,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609180</v>
+        <v>609248</v>
       </c>
       <c r="R34" t="n">
-        <v>7017969</v>
+        <v>7018303</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124836709</v>
+        <v>124839286</v>
       </c>
       <c r="B35" t="n">
         <v>91299</v>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609251</v>
+        <v>609042</v>
       </c>
       <c r="R35" t="n">
-        <v>7018241</v>
+        <v>7018085</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124839286</v>
+        <v>124840385</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,38 +4294,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609042</v>
+        <v>609100</v>
       </c>
       <c r="R36" t="n">
-        <v>7018085</v>
+        <v>7018053</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4384,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124835668</v>
+        <v>124836709</v>
       </c>
       <c r="B37" t="n">
         <v>91299</v>
@@ -4424,10 +4428,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609359</v>
+        <v>609251</v>
       </c>
       <c r="R37" t="n">
-        <v>7018158</v>
+        <v>7018241</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4486,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124840385</v>
+        <v>124835668</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4498,42 +4502,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609100</v>
+        <v>609359</v>
       </c>
       <c r="R38" t="n">
-        <v>7018053</v>
+        <v>7018158</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124836744</v>
+        <v>124837159</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609243</v>
+        <v>609248</v>
       </c>
       <c r="R6" t="n">
-        <v>7018254</v>
+        <v>7018303</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124835740</v>
+        <v>124839525</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,25 +1313,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609356</v>
+        <v>609068</v>
       </c>
       <c r="R7" t="n">
-        <v>7018141</v>
+        <v>7018108</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124836321</v>
+        <v>124837151</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609324</v>
+        <v>609253</v>
       </c>
       <c r="R8" t="n">
-        <v>7018195</v>
+        <v>7018298</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124841120</v>
+        <v>124837411</v>
       </c>
       <c r="B9" t="n">
         <v>91012</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609178</v>
+        <v>609251</v>
       </c>
       <c r="R9" t="n">
-        <v>7017968</v>
+        <v>7018311</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124837151</v>
+        <v>124837331</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,25 +1619,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609253</v>
+        <v>609236</v>
       </c>
       <c r="R10" t="n">
-        <v>7018298</v>
+        <v>7018288</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124839525</v>
+        <v>124836709</v>
       </c>
       <c r="B11" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609068</v>
+        <v>609251</v>
       </c>
       <c r="R11" t="n">
-        <v>7018108</v>
+        <v>7018241</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124837411</v>
+        <v>124841120</v>
       </c>
       <c r="B12" t="n">
         <v>91012</v>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609251</v>
+        <v>609178</v>
       </c>
       <c r="R12" t="n">
-        <v>7018311</v>
+        <v>7017968</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836317</v>
+        <v>124841153</v>
       </c>
       <c r="B13" t="n">
         <v>91299</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609320</v>
+        <v>609180</v>
       </c>
       <c r="R13" t="n">
-        <v>7018199</v>
+        <v>7017969</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124835873</v>
+        <v>124837429</v>
       </c>
       <c r="B14" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,25 +2027,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609372</v>
+        <v>609251</v>
       </c>
       <c r="R14" t="n">
-        <v>7018137</v>
+        <v>7018311</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124838979</v>
+        <v>124840461</v>
       </c>
       <c r="B16" t="n">
         <v>91299</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609132</v>
+        <v>609114</v>
       </c>
       <c r="R16" t="n">
-        <v>7018018</v>
+        <v>7018022</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124837223</v>
+        <v>124837340</v>
       </c>
       <c r="B17" t="n">
-        <v>91026</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,25 +2333,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609229</v>
+        <v>609241</v>
       </c>
       <c r="R17" t="n">
-        <v>7018310</v>
+        <v>7018298</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124836692</v>
+        <v>124838979</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,25 +2435,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609259</v>
+        <v>609132</v>
       </c>
       <c r="R18" t="n">
-        <v>7018252</v>
+        <v>7018018</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124836147</v>
+        <v>124840385</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,38 +2537,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609334</v>
+        <v>609100</v>
       </c>
       <c r="R19" t="n">
-        <v>7018163</v>
+        <v>7018053</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2627,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124838762</v>
+        <v>124836351</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,38 +2647,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609202</v>
+        <v>609330</v>
       </c>
       <c r="R20" t="n">
-        <v>7018017</v>
+        <v>7018199</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124837340</v>
+        <v>124839286</v>
       </c>
       <c r="B21" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,25 +2745,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609241</v>
+        <v>609042</v>
       </c>
       <c r="R21" t="n">
-        <v>7018298</v>
+        <v>7018085</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838913</v>
+        <v>124839318</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609144</v>
+        <v>609091</v>
       </c>
       <c r="R22" t="n">
-        <v>7018039</v>
+        <v>7018078</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124837331</v>
+        <v>124836317</v>
       </c>
       <c r="B23" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609236</v>
+        <v>609320</v>
       </c>
       <c r="R23" t="n">
-        <v>7018288</v>
+        <v>7018199</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124839318</v>
+        <v>124837223</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609091</v>
+        <v>609229</v>
       </c>
       <c r="R24" t="n">
-        <v>7018078</v>
+        <v>7018310</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124841283</v>
+        <v>124836692</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,42 +3153,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609215</v>
+        <v>609259</v>
       </c>
       <c r="R25" t="n">
-        <v>7017959</v>
+        <v>7018252</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3247,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838903</v>
+        <v>124836828</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3287,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609168</v>
+        <v>609243</v>
       </c>
       <c r="R26" t="n">
-        <v>7018021</v>
+        <v>7018223</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3349,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124836351</v>
+        <v>124835740</v>
       </c>
       <c r="B27" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3361,25 +3357,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609330</v>
+        <v>609356</v>
       </c>
       <c r="R27" t="n">
-        <v>7018199</v>
+        <v>7018141</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3451,10 +3447,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124836828</v>
+        <v>124841439</v>
       </c>
       <c r="B28" t="n">
-        <v>90962</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,28 +3459,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
@@ -3494,7 +3494,7 @@
         <v>609243</v>
       </c>
       <c r="R28" t="n">
-        <v>7018223</v>
+        <v>7017992</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124836811</v>
+        <v>124836321</v>
       </c>
       <c r="B29" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609241</v>
+        <v>609324</v>
       </c>
       <c r="R29" t="n">
-        <v>7018250</v>
+        <v>7018195</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124837429</v>
+        <v>124836744</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R30" t="n">
-        <v>7018311</v>
+        <v>7018254</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124840461</v>
+        <v>124835873</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,25 +3769,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609114</v>
+        <v>609372</v>
       </c>
       <c r="R31" t="n">
-        <v>7018022</v>
+        <v>7018137</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3859,7 +3859,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124841153</v>
+        <v>124836147</v>
       </c>
       <c r="B32" t="n">
         <v>91299</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609180</v>
+        <v>609334</v>
       </c>
       <c r="R32" t="n">
-        <v>7017969</v>
+        <v>7018163</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4078,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124837159</v>
+        <v>124835668</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4094,21 +4094,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609248</v>
+        <v>609359</v>
       </c>
       <c r="R34" t="n">
-        <v>7018303</v>
+        <v>7018158</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4180,10 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124839286</v>
+        <v>124838903</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609042</v>
+        <v>609168</v>
       </c>
       <c r="R35" t="n">
-        <v>7018085</v>
+        <v>7018021</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124840385</v>
+        <v>124838913</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,42 +4294,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609100</v>
+        <v>609144</v>
       </c>
       <c r="R36" t="n">
-        <v>7018053</v>
+        <v>7018039</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4388,10 +4384,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124836709</v>
+        <v>124841283</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4400,38 +4396,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609251</v>
+        <v>609215</v>
       </c>
       <c r="R37" t="n">
-        <v>7018241</v>
+        <v>7017959</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124835668</v>
+        <v>124838762</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4502,38 +4502,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609359</v>
+        <v>609202</v>
       </c>
       <c r="R38" t="n">
-        <v>7018158</v>
+        <v>7018017</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4592,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124841439</v>
+        <v>124836811</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,38 +4612,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609243</v>
+        <v>609241</v>
       </c>
       <c r="R39" t="n">
-        <v>7017992</v>
+        <v>7018250</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124837159</v>
+        <v>124836351</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609248</v>
+        <v>609330</v>
       </c>
       <c r="R6" t="n">
-        <v>7018303</v>
+        <v>7018199</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124839525</v>
+        <v>124836317</v>
       </c>
       <c r="B7" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,25 +1313,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609068</v>
+        <v>609320</v>
       </c>
       <c r="R7" t="n">
-        <v>7018108</v>
+        <v>7018199</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124837151</v>
+        <v>124840385</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,38 +1415,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609253</v>
+        <v>609100</v>
       </c>
       <c r="R8" t="n">
-        <v>7018298</v>
+        <v>7018053</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,7 +1509,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124837411</v>
+        <v>124841120</v>
       </c>
       <c r="B9" t="n">
         <v>91012</v>
@@ -1545,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609251</v>
+        <v>609178</v>
       </c>
       <c r="R9" t="n">
-        <v>7018311</v>
+        <v>7017968</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124837331</v>
+        <v>124839307</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,25 +1623,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609236</v>
+        <v>609077</v>
       </c>
       <c r="R10" t="n">
-        <v>7018288</v>
+        <v>7018074</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124836709</v>
+        <v>124836692</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1725,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609251</v>
+        <v>609259</v>
       </c>
       <c r="R11" t="n">
-        <v>7018241</v>
+        <v>7018252</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124841120</v>
+        <v>124835707</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91413</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,25 +1827,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609178</v>
+        <v>609360</v>
       </c>
       <c r="R12" t="n">
-        <v>7017968</v>
+        <v>7018137</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1897,6 +1901,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1913,7 +1932,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124841153</v>
+        <v>124840461</v>
       </c>
       <c r="B13" t="n">
         <v>91299</v>
@@ -1953,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609180</v>
+        <v>609114</v>
       </c>
       <c r="R13" t="n">
-        <v>7017969</v>
+        <v>7018022</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124837429</v>
+        <v>124837151</v>
       </c>
       <c r="B14" t="n">
         <v>91299</v>
@@ -2055,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609251</v>
+        <v>609253</v>
       </c>
       <c r="R14" t="n">
-        <v>7018311</v>
+        <v>7018298</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,7 +2136,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124839307</v>
+        <v>124838979</v>
       </c>
       <c r="B15" t="n">
         <v>91299</v>
@@ -2157,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609077</v>
+        <v>609132</v>
       </c>
       <c r="R15" t="n">
-        <v>7018074</v>
+        <v>7018018</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124840461</v>
+        <v>124837340</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,25 +2250,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609114</v>
+        <v>609241</v>
       </c>
       <c r="R16" t="n">
-        <v>7018022</v>
+        <v>7018298</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124837340</v>
+        <v>124838762</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,38 +2352,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609241</v>
+        <v>609202</v>
       </c>
       <c r="R17" t="n">
-        <v>7018298</v>
+        <v>7018017</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124838979</v>
+        <v>124836828</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,21 +2462,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609132</v>
+        <v>609243</v>
       </c>
       <c r="R18" t="n">
-        <v>7018018</v>
+        <v>7018223</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2525,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124840385</v>
+        <v>124836744</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,42 +2560,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609100</v>
+        <v>609243</v>
       </c>
       <c r="R19" t="n">
-        <v>7018053</v>
+        <v>7018254</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2631,10 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124836351</v>
+        <v>124836709</v>
       </c>
       <c r="B20" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,25 +2662,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609330</v>
+        <v>609251</v>
       </c>
       <c r="R20" t="n">
-        <v>7018199</v>
+        <v>7018241</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2733,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124839286</v>
+        <v>124837331</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,25 +2764,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609042</v>
+        <v>609236</v>
       </c>
       <c r="R21" t="n">
-        <v>7018085</v>
+        <v>7018288</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,10 +2854,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124839318</v>
+        <v>124836147</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,21 +2870,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609091</v>
+        <v>609334</v>
       </c>
       <c r="R22" t="n">
-        <v>7018078</v>
+        <v>7018163</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2937,10 +2956,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124836317</v>
+        <v>124835740</v>
       </c>
       <c r="B23" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2972,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609320</v>
+        <v>609356</v>
       </c>
       <c r="R23" t="n">
-        <v>7018199</v>
+        <v>7018141</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3039,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124837223</v>
+        <v>124838913</v>
       </c>
       <c r="B24" t="n">
-        <v>91026</v>
+        <v>91299</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,21 +3074,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3098,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609229</v>
+        <v>609144</v>
       </c>
       <c r="R24" t="n">
-        <v>7018310</v>
+        <v>7018039</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3141,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124836692</v>
+        <v>124837429</v>
       </c>
       <c r="B25" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,25 +3172,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3181,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609259</v>
+        <v>609251</v>
       </c>
       <c r="R25" t="n">
-        <v>7018252</v>
+        <v>7018311</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3243,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124836828</v>
+        <v>124839525</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>91673</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3255,25 +3274,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>898</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3283,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609243</v>
+        <v>609068</v>
       </c>
       <c r="R26" t="n">
-        <v>7018223</v>
+        <v>7018108</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3345,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124835740</v>
+        <v>124841153</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3361,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609356</v>
+        <v>609180</v>
       </c>
       <c r="R27" t="n">
-        <v>7018141</v>
+        <v>7017969</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3447,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124841439</v>
+        <v>124836811</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,38 +3482,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609243</v>
+        <v>609241</v>
       </c>
       <c r="R28" t="n">
-        <v>7017992</v>
+        <v>7018250</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3553,10 +3568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124836321</v>
+        <v>124835668</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,21 +3584,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3593,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609324</v>
+        <v>609359</v>
       </c>
       <c r="R29" t="n">
-        <v>7018195</v>
+        <v>7018158</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3655,7 +3670,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124836744</v>
+        <v>124838903</v>
       </c>
       <c r="B30" t="n">
         <v>91012</v>
@@ -3695,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609243</v>
+        <v>609168</v>
       </c>
       <c r="R30" t="n">
-        <v>7018254</v>
+        <v>7018021</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3757,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124835873</v>
+        <v>124839286</v>
       </c>
       <c r="B31" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,25 +3784,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3797,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609372</v>
+        <v>609042</v>
       </c>
       <c r="R31" t="n">
-        <v>7018137</v>
+        <v>7018085</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3859,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124836147</v>
+        <v>124841439</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,38 +3886,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609334</v>
+        <v>609243</v>
       </c>
       <c r="R32" t="n">
-        <v>7018163</v>
+        <v>7017992</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3961,10 +3980,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124835707</v>
+        <v>124839318</v>
       </c>
       <c r="B33" t="n">
-        <v>91413</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,25 +3992,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4001,10 +4020,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609360</v>
+        <v>609091</v>
       </c>
       <c r="R33" t="n">
-        <v>7018137</v>
+        <v>7018078</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4047,21 +4066,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4078,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124835668</v>
+        <v>124836321</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4094,21 +4098,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4118,10 +4122,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609359</v>
+        <v>609324</v>
       </c>
       <c r="R34" t="n">
-        <v>7018158</v>
+        <v>7018195</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4180,10 +4184,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124838903</v>
+        <v>124841283</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,38 +4196,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609168</v>
+        <v>609215</v>
       </c>
       <c r="R35" t="n">
-        <v>7018021</v>
+        <v>7017959</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4282,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124838913</v>
+        <v>124837223</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4298,21 +4306,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4322,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609144</v>
+        <v>609229</v>
       </c>
       <c r="R36" t="n">
-        <v>7018039</v>
+        <v>7018310</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4384,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124841283</v>
+        <v>124837159</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4396,42 +4404,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609215</v>
+        <v>609248</v>
       </c>
       <c r="R37" t="n">
-        <v>7017959</v>
+        <v>7018303</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4490,10 +4494,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124838762</v>
+        <v>124837411</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4502,42 +4506,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609202</v>
+        <v>609251</v>
       </c>
       <c r="R38" t="n">
-        <v>7018017</v>
+        <v>7018311</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124836811</v>
+        <v>124835873</v>
       </c>
       <c r="B39" t="n">
-        <v>91361</v>
+        <v>91673</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4612,21 +4612,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>898</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609241</v>
+        <v>609372</v>
       </c>
       <c r="R39" t="n">
-        <v>7018250</v>
+        <v>7018137</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124836351</v>
+        <v>124838913</v>
       </c>
       <c r="B6" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609330</v>
+        <v>609144</v>
       </c>
       <c r="R6" t="n">
-        <v>7018199</v>
+        <v>7018039</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124840385</v>
+        <v>124837223</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91026</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,42 +1415,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609100</v>
+        <v>609229</v>
       </c>
       <c r="R8" t="n">
-        <v>7018053</v>
+        <v>7018310</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1509,7 +1505,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124841120</v>
+        <v>124836744</v>
       </c>
       <c r="B9" t="n">
         <v>91012</v>
@@ -1549,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609178</v>
+        <v>609243</v>
       </c>
       <c r="R9" t="n">
-        <v>7017968</v>
+        <v>7018254</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1611,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124839307</v>
+        <v>124836828</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609077</v>
+        <v>609243</v>
       </c>
       <c r="R10" t="n">
-        <v>7018074</v>
+        <v>7018223</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1713,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124836692</v>
+        <v>124841120</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609259</v>
+        <v>609178</v>
       </c>
       <c r="R11" t="n">
-        <v>7018252</v>
+        <v>7017968</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1815,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124835707</v>
+        <v>124838903</v>
       </c>
       <c r="B12" t="n">
-        <v>91413</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,25 +1823,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609360</v>
+        <v>609168</v>
       </c>
       <c r="R12" t="n">
-        <v>7018137</v>
+        <v>7018021</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1901,21 +1897,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1932,7 +1913,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124840461</v>
+        <v>124836709</v>
       </c>
       <c r="B13" t="n">
         <v>91299</v>
@@ -1972,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609114</v>
+        <v>609251</v>
       </c>
       <c r="R13" t="n">
-        <v>7018022</v>
+        <v>7018241</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2034,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124837151</v>
+        <v>124839525</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2027,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609253</v>
+        <v>609068</v>
       </c>
       <c r="R14" t="n">
-        <v>7018298</v>
+        <v>7018108</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2136,7 +2117,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124838979</v>
+        <v>124839307</v>
       </c>
       <c r="B15" t="n">
         <v>91299</v>
@@ -2176,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609132</v>
+        <v>609077</v>
       </c>
       <c r="R15" t="n">
-        <v>7018018</v>
+        <v>7018074</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2238,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124837340</v>
+        <v>124837159</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,25 +2231,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609241</v>
+        <v>609248</v>
       </c>
       <c r="R16" t="n">
-        <v>7018298</v>
+        <v>7018303</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2340,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124838762</v>
+        <v>124837411</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,42 +2333,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609202</v>
+        <v>609251</v>
       </c>
       <c r="R17" t="n">
-        <v>7018017</v>
+        <v>7018311</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2446,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124836828</v>
+        <v>124836811</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>91361</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,25 +2435,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2486,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609243</v>
+        <v>609241</v>
       </c>
       <c r="R18" t="n">
-        <v>7018223</v>
+        <v>7018250</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2548,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124836744</v>
+        <v>124837340</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,25 +2537,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2588,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609243</v>
+        <v>609241</v>
       </c>
       <c r="R19" t="n">
-        <v>7018254</v>
+        <v>7018298</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2650,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124836709</v>
+        <v>124839318</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,21 +2643,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2690,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609251</v>
+        <v>609091</v>
       </c>
       <c r="R20" t="n">
-        <v>7018241</v>
+        <v>7018078</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2752,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124837331</v>
+        <v>124835707</v>
       </c>
       <c r="B21" t="n">
-        <v>91361</v>
+        <v>91413</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2764,25 +2741,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>4217</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2792,10 +2769,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609236</v>
+        <v>609360</v>
       </c>
       <c r="R21" t="n">
-        <v>7018288</v>
+        <v>7018137</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2838,6 +2815,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2854,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124836147</v>
+        <v>124841439</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2866,38 +2858,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609334</v>
+        <v>609243</v>
       </c>
       <c r="R22" t="n">
-        <v>7018163</v>
+        <v>7017992</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2956,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124835740</v>
+        <v>124840385</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,38 +2964,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609356</v>
+        <v>609100</v>
       </c>
       <c r="R23" t="n">
-        <v>7018141</v>
+        <v>7018053</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838913</v>
+        <v>124836351</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3070,25 +3070,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609144</v>
+        <v>609330</v>
       </c>
       <c r="R24" t="n">
-        <v>7018039</v>
+        <v>7018199</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124837429</v>
+        <v>124838979</v>
       </c>
       <c r="B25" t="n">
         <v>91299</v>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609251</v>
+        <v>609132</v>
       </c>
       <c r="R25" t="n">
-        <v>7018311</v>
+        <v>7018018</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124839525</v>
+        <v>124836692</v>
       </c>
       <c r="B26" t="n">
-        <v>91673</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,25 +3274,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609068</v>
+        <v>609259</v>
       </c>
       <c r="R26" t="n">
-        <v>7018108</v>
+        <v>7018252</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124841153</v>
+        <v>124835873</v>
       </c>
       <c r="B27" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3376,25 +3376,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609180</v>
+        <v>609372</v>
       </c>
       <c r="R27" t="n">
-        <v>7017969</v>
+        <v>7018137</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124836811</v>
+        <v>124837331</v>
       </c>
       <c r="B28" t="n">
         <v>91361</v>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609241</v>
+        <v>609236</v>
       </c>
       <c r="R28" t="n">
-        <v>7018250</v>
+        <v>7018288</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124835668</v>
+        <v>124840461</v>
       </c>
       <c r="B29" t="n">
         <v>91299</v>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609359</v>
+        <v>609114</v>
       </c>
       <c r="R29" t="n">
-        <v>7018158</v>
+        <v>7018022</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838903</v>
+        <v>124835668</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609168</v>
+        <v>609359</v>
       </c>
       <c r="R30" t="n">
-        <v>7018021</v>
+        <v>7018158</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124839286</v>
+        <v>124838762</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,38 +3784,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609042</v>
+        <v>609202</v>
       </c>
       <c r="R31" t="n">
-        <v>7018085</v>
+        <v>7018017</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3874,7 +3878,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124841439</v>
+        <v>124841283</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -3909,7 +3913,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3918,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609243</v>
+        <v>609215</v>
       </c>
       <c r="R32" t="n">
-        <v>7017992</v>
+        <v>7017959</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3980,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124839318</v>
+        <v>124841153</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3996,21 +4000,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4020,10 +4024,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609091</v>
+        <v>609180</v>
       </c>
       <c r="R33" t="n">
-        <v>7018078</v>
+        <v>7017969</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4184,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124841283</v>
+        <v>124835740</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4196,42 +4200,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609215</v>
+        <v>609356</v>
       </c>
       <c r="R35" t="n">
-        <v>7017959</v>
+        <v>7018141</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124837223</v>
+        <v>124837151</v>
       </c>
       <c r="B36" t="n">
-        <v>91026</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609229</v>
+        <v>609253</v>
       </c>
       <c r="R36" t="n">
-        <v>7018310</v>
+        <v>7018298</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124837159</v>
+        <v>124836147</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4408,21 +4408,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609248</v>
+        <v>609334</v>
       </c>
       <c r="R37" t="n">
-        <v>7018303</v>
+        <v>7018163</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124837411</v>
+        <v>124839286</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609251</v>
+        <v>609042</v>
       </c>
       <c r="R38" t="n">
-        <v>7018311</v>
+        <v>7018085</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124835873</v>
+        <v>124837429</v>
       </c>
       <c r="B39" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,25 +4608,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609372</v>
+        <v>609251</v>
       </c>
       <c r="R39" t="n">
-        <v>7018137</v>
+        <v>7018311</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836709</v>
+        <v>124839525</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,25 +1925,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609251</v>
+        <v>609068</v>
       </c>
       <c r="R13" t="n">
-        <v>7018241</v>
+        <v>7018108</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124839525</v>
+        <v>124836709</v>
       </c>
       <c r="B14" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,25 +2027,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609068</v>
+        <v>609251</v>
       </c>
       <c r="R14" t="n">
-        <v>7018108</v>
+        <v>7018241</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838979</v>
+        <v>124836692</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,25 +3172,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609132</v>
+        <v>609259</v>
       </c>
       <c r="R25" t="n">
-        <v>7018018</v>
+        <v>7018252</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124836692</v>
+        <v>124838979</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,25 +3274,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609259</v>
+        <v>609132</v>
       </c>
       <c r="R26" t="n">
-        <v>7018252</v>
+        <v>7018018</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124837331</v>
+        <v>124840461</v>
       </c>
       <c r="B28" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,25 +3478,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609236</v>
+        <v>609114</v>
       </c>
       <c r="R28" t="n">
-        <v>7018288</v>
+        <v>7018022</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124840461</v>
+        <v>124835668</v>
       </c>
       <c r="B29" t="n">
         <v>91299</v>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609114</v>
+        <v>609359</v>
       </c>
       <c r="R29" t="n">
-        <v>7018022</v>
+        <v>7018158</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124835668</v>
+        <v>124837331</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,25 +3682,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609359</v>
+        <v>609236</v>
       </c>
       <c r="R30" t="n">
-        <v>7018158</v>
+        <v>7018288</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124839525</v>
+        <v>124836709</v>
       </c>
       <c r="B13" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,25 +1925,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609068</v>
+        <v>609251</v>
       </c>
       <c r="R13" t="n">
-        <v>7018108</v>
+        <v>7018241</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124836709</v>
+        <v>124839525</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,25 +2027,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609251</v>
+        <v>609068</v>
       </c>
       <c r="R14" t="n">
-        <v>7018241</v>
+        <v>7018108</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124836692</v>
+        <v>124838979</v>
       </c>
       <c r="B25" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,25 +3172,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609259</v>
+        <v>609132</v>
       </c>
       <c r="R25" t="n">
-        <v>7018252</v>
+        <v>7018018</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124838979</v>
+        <v>124836692</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,25 +3274,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609132</v>
+        <v>609259</v>
       </c>
       <c r="R26" t="n">
-        <v>7018018</v>
+        <v>7018252</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124840461</v>
+        <v>124838762</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,38 +3478,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609114</v>
+        <v>609202</v>
       </c>
       <c r="R28" t="n">
-        <v>7018022</v>
+        <v>7018017</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3568,10 +3572,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124835668</v>
+        <v>124841283</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3580,38 +3584,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609359</v>
+        <v>609215</v>
       </c>
       <c r="R29" t="n">
-        <v>7018158</v>
+        <v>7017959</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3670,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124837331</v>
+        <v>124840461</v>
       </c>
       <c r="B30" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,25 +3690,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3718,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609236</v>
+        <v>609114</v>
       </c>
       <c r="R30" t="n">
-        <v>7018288</v>
+        <v>7018022</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3772,10 +3780,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124838762</v>
+        <v>124835668</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,42 +3792,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609202</v>
+        <v>609359</v>
       </c>
       <c r="R31" t="n">
-        <v>7018017</v>
+        <v>7018158</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3878,10 +3882,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124841283</v>
+        <v>124837331</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3894,38 +3898,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609215</v>
+        <v>609236</v>
       </c>
       <c r="R32" t="n">
-        <v>7017959</v>
+        <v>7018288</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124838913</v>
+        <v>124836828</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609144</v>
+        <v>609243</v>
       </c>
       <c r="R6" t="n">
-        <v>7018039</v>
+        <v>7018223</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124836317</v>
+        <v>124835668</v>
       </c>
       <c r="B7" t="n">
         <v>91299</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609320</v>
+        <v>609359</v>
       </c>
       <c r="R7" t="n">
-        <v>7018199</v>
+        <v>7018158</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124837223</v>
+        <v>124841120</v>
       </c>
       <c r="B8" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609229</v>
+        <v>609178</v>
       </c>
       <c r="R8" t="n">
-        <v>7018310</v>
+        <v>7017968</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124836744</v>
+        <v>124836321</v>
       </c>
       <c r="B9" t="n">
         <v>91012</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609243</v>
+        <v>609324</v>
       </c>
       <c r="R9" t="n">
-        <v>7018254</v>
+        <v>7018195</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124836828</v>
+        <v>124836709</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,21 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609243</v>
+        <v>609251</v>
       </c>
       <c r="R10" t="n">
-        <v>7018223</v>
+        <v>7018241</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124841120</v>
+        <v>124836317</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609178</v>
+        <v>609320</v>
       </c>
       <c r="R11" t="n">
-        <v>7017968</v>
+        <v>7018199</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124838903</v>
+        <v>124836147</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609168</v>
+        <v>609334</v>
       </c>
       <c r="R12" t="n">
-        <v>7018021</v>
+        <v>7018163</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836709</v>
+        <v>124839525</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,25 +1925,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609251</v>
+        <v>609068</v>
       </c>
       <c r="R13" t="n">
-        <v>7018241</v>
+        <v>7018108</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124839525</v>
+        <v>124841283</v>
       </c>
       <c r="B14" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,34 +2031,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609068</v>
+        <v>609215</v>
       </c>
       <c r="R14" t="n">
-        <v>7018108</v>
+        <v>7017959</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124839307</v>
+        <v>124837411</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,21 +2137,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609077</v>
+        <v>609251</v>
       </c>
       <c r="R15" t="n">
-        <v>7018074</v>
+        <v>7018311</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124837159</v>
+        <v>124839286</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,21 +2239,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609248</v>
+        <v>609042</v>
       </c>
       <c r="R16" t="n">
-        <v>7018303</v>
+        <v>7018085</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,7 +2325,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124837411</v>
+        <v>124836744</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2361,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R17" t="n">
-        <v>7018311</v>
+        <v>7018254</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124836811</v>
+        <v>124835740</v>
       </c>
       <c r="B18" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,25 +2439,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609241</v>
+        <v>609356</v>
       </c>
       <c r="R18" t="n">
-        <v>7018250</v>
+        <v>7018141</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2627,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124839318</v>
+        <v>124838762</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,38 +2643,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609091</v>
+        <v>609202</v>
       </c>
       <c r="R20" t="n">
-        <v>7018078</v>
+        <v>7018017</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2729,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124835707</v>
+        <v>124836692</v>
       </c>
       <c r="B21" t="n">
-        <v>91413</v>
+        <v>90977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,21 +2753,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2769,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609360</v>
+        <v>609259</v>
       </c>
       <c r="R21" t="n">
-        <v>7018137</v>
+        <v>7018252</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2815,21 +2823,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2846,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124841439</v>
+        <v>124838903</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2858,42 +2851,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609243</v>
+        <v>609168</v>
       </c>
       <c r="R22" t="n">
-        <v>7017992</v>
+        <v>7018021</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2952,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124840385</v>
+        <v>124837159</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,42 +2953,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609100</v>
+        <v>609248</v>
       </c>
       <c r="R23" t="n">
-        <v>7018053</v>
+        <v>7018303</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3058,7 +3043,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124836351</v>
+        <v>124837331</v>
       </c>
       <c r="B24" t="n">
         <v>91361</v>
@@ -3098,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609330</v>
+        <v>609236</v>
       </c>
       <c r="R24" t="n">
-        <v>7018199</v>
+        <v>7018288</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3160,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838979</v>
+        <v>124841439</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,38 +3157,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609132</v>
+        <v>609243</v>
       </c>
       <c r="R25" t="n">
-        <v>7018018</v>
+        <v>7017992</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3262,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124836692</v>
+        <v>124840461</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,25 +3263,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3302,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609259</v>
+        <v>609114</v>
       </c>
       <c r="R26" t="n">
-        <v>7018252</v>
+        <v>7018022</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3364,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124835873</v>
+        <v>124837223</v>
       </c>
       <c r="B27" t="n">
-        <v>91673</v>
+        <v>91026</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3376,25 +3365,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609372</v>
+        <v>609229</v>
       </c>
       <c r="R27" t="n">
-        <v>7018137</v>
+        <v>7018310</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3466,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838762</v>
+        <v>124841153</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,42 +3467,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609202</v>
+        <v>609180</v>
       </c>
       <c r="R28" t="n">
-        <v>7018017</v>
+        <v>7017969</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3572,7 +3557,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124841283</v>
+        <v>124840385</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3616,10 +3601,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609215</v>
+        <v>609100</v>
       </c>
       <c r="R29" t="n">
-        <v>7017959</v>
+        <v>7018053</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3678,7 +3663,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124840461</v>
+        <v>124838913</v>
       </c>
       <c r="B30" t="n">
         <v>91299</v>
@@ -3718,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609114</v>
+        <v>609144</v>
       </c>
       <c r="R30" t="n">
-        <v>7018022</v>
+        <v>7018039</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3780,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124835668</v>
+        <v>124836811</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3792,25 +3777,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3820,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609359</v>
+        <v>609241</v>
       </c>
       <c r="R31" t="n">
-        <v>7018158</v>
+        <v>7018250</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3882,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124837331</v>
+        <v>124835707</v>
       </c>
       <c r="B32" t="n">
-        <v>91361</v>
+        <v>91413</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3894,25 +3879,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>4217</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3922,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609236</v>
+        <v>609360</v>
       </c>
       <c r="R32" t="n">
-        <v>7018288</v>
+        <v>7018137</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3968,6 +3953,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3984,7 +3984,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124841153</v>
+        <v>124837429</v>
       </c>
       <c r="B33" t="n">
         <v>91299</v>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609180</v>
+        <v>609251</v>
       </c>
       <c r="R33" t="n">
-        <v>7017969</v>
+        <v>7018311</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124836321</v>
+        <v>124836351</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4098,25 +4098,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609324</v>
+        <v>609330</v>
       </c>
       <c r="R34" t="n">
-        <v>7018195</v>
+        <v>7018199</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124835740</v>
+        <v>124839307</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4204,21 +4204,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609356</v>
+        <v>609077</v>
       </c>
       <c r="R35" t="n">
-        <v>7018141</v>
+        <v>7018074</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124836147</v>
+        <v>124838979</v>
       </c>
       <c r="B37" t="n">
         <v>91299</v>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609334</v>
+        <v>609132</v>
       </c>
       <c r="R37" t="n">
-        <v>7018163</v>
+        <v>7018018</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124839286</v>
+        <v>124839318</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609042</v>
+        <v>609091</v>
       </c>
       <c r="R38" t="n">
-        <v>7018085</v>
+        <v>7018078</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124837429</v>
+        <v>124835873</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,25 +4608,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609251</v>
+        <v>609372</v>
       </c>
       <c r="R39" t="n">
-        <v>7018311</v>
+        <v>7018137</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124836828</v>
+        <v>124837411</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609243</v>
+        <v>609251</v>
       </c>
       <c r="R6" t="n">
-        <v>7018223</v>
+        <v>7018311</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124835668</v>
+        <v>124836351</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,25 +1313,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609359</v>
+        <v>609330</v>
       </c>
       <c r="R7" t="n">
-        <v>7018158</v>
+        <v>7018199</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124841120</v>
+        <v>124840461</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609178</v>
+        <v>609114</v>
       </c>
       <c r="R8" t="n">
-        <v>7017968</v>
+        <v>7018022</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124836321</v>
+        <v>124836147</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609324</v>
+        <v>609334</v>
       </c>
       <c r="R9" t="n">
-        <v>7018195</v>
+        <v>7018163</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124836709</v>
+        <v>124841153</v>
       </c>
       <c r="B10" t="n">
         <v>91299</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609251</v>
+        <v>609180</v>
       </c>
       <c r="R10" t="n">
-        <v>7018241</v>
+        <v>7017969</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124836317</v>
+        <v>124841120</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609320</v>
+        <v>609178</v>
       </c>
       <c r="R11" t="n">
-        <v>7018199</v>
+        <v>7017968</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124836147</v>
+        <v>124836321</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609334</v>
+        <v>609324</v>
       </c>
       <c r="R12" t="n">
-        <v>7018163</v>
+        <v>7018195</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124839525</v>
+        <v>124836828</v>
       </c>
       <c r="B13" t="n">
-        <v>91673</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,25 +1925,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>898</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609068</v>
+        <v>609243</v>
       </c>
       <c r="R13" t="n">
-        <v>7018108</v>
+        <v>7018223</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124841283</v>
+        <v>124836811</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,38 +2031,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609215</v>
+        <v>609241</v>
       </c>
       <c r="R14" t="n">
-        <v>7017959</v>
+        <v>7018250</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124837411</v>
+        <v>124837151</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,21 +2133,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609251</v>
+        <v>609253</v>
       </c>
       <c r="R15" t="n">
-        <v>7018311</v>
+        <v>7018298</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2223,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124839286</v>
+        <v>124837159</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2263,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609042</v>
+        <v>609248</v>
       </c>
       <c r="R16" t="n">
-        <v>7018085</v>
+        <v>7018303</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2325,7 +2321,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124836744</v>
+        <v>124838903</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2365,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609243</v>
+        <v>609168</v>
       </c>
       <c r="R17" t="n">
-        <v>7018254</v>
+        <v>7018021</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2427,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124835740</v>
+        <v>124835707</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>91413</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,25 +2435,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609356</v>
+        <v>609360</v>
       </c>
       <c r="R18" t="n">
-        <v>7018141</v>
+        <v>7018137</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2513,6 +2509,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2529,10 +2540,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124837340</v>
+        <v>124835668</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,25 +2552,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2580,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609241</v>
+        <v>609359</v>
       </c>
       <c r="R19" t="n">
-        <v>7018298</v>
+        <v>7018158</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2631,10 +2642,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124838762</v>
+        <v>124839286</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,42 +2654,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609202</v>
+        <v>609042</v>
       </c>
       <c r="R20" t="n">
-        <v>7018017</v>
+        <v>7018085</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2737,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124836692</v>
+        <v>124836317</v>
       </c>
       <c r="B21" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,25 +2756,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2777,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609259</v>
+        <v>609320</v>
       </c>
       <c r="R21" t="n">
-        <v>7018252</v>
+        <v>7018199</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2839,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124838903</v>
+        <v>124839307</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2879,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609168</v>
+        <v>609077</v>
       </c>
       <c r="R22" t="n">
-        <v>7018021</v>
+        <v>7018074</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2941,7 +2948,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124837159</v>
+        <v>124839318</v>
       </c>
       <c r="B23" t="n">
         <v>91012</v>
@@ -2981,10 +2988,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609248</v>
+        <v>609091</v>
       </c>
       <c r="R23" t="n">
-        <v>7018303</v>
+        <v>7018078</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3043,10 +3050,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124837331</v>
+        <v>124841283</v>
       </c>
       <c r="B24" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,34 +3066,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609236</v>
+        <v>609215</v>
       </c>
       <c r="R24" t="n">
-        <v>7018288</v>
+        <v>7017959</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3145,7 +3156,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124841439</v>
+        <v>124840385</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3180,7 +3191,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3189,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609243</v>
+        <v>609100</v>
       </c>
       <c r="R25" t="n">
-        <v>7017992</v>
+        <v>7018053</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3251,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124840461</v>
+        <v>124837223</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,21 +3278,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3291,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609114</v>
+        <v>609229</v>
       </c>
       <c r="R26" t="n">
-        <v>7018022</v>
+        <v>7018310</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3353,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124837223</v>
+        <v>124836744</v>
       </c>
       <c r="B27" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3369,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3393,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609229</v>
+        <v>609243</v>
       </c>
       <c r="R27" t="n">
-        <v>7018310</v>
+        <v>7018254</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3455,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124841153</v>
+        <v>124835873</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,25 +3478,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609180</v>
+        <v>609372</v>
       </c>
       <c r="R28" t="n">
-        <v>7017969</v>
+        <v>7018137</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3557,10 +3568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124840385</v>
+        <v>124837340</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,42 +3580,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609100</v>
+        <v>609241</v>
       </c>
       <c r="R29" t="n">
-        <v>7018053</v>
+        <v>7018298</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3663,7 +3670,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838913</v>
+        <v>124838979</v>
       </c>
       <c r="B30" t="n">
         <v>91299</v>
@@ -3703,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609144</v>
+        <v>609132</v>
       </c>
       <c r="R30" t="n">
-        <v>7018039</v>
+        <v>7018018</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3765,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124836811</v>
+        <v>124836692</v>
       </c>
       <c r="B31" t="n">
-        <v>91361</v>
+        <v>90977</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3777,25 +3784,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609241</v>
+        <v>609259</v>
       </c>
       <c r="R31" t="n">
-        <v>7018250</v>
+        <v>7018252</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3867,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124835707</v>
+        <v>124835740</v>
       </c>
       <c r="B32" t="n">
-        <v>91413</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3879,25 +3886,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609360</v>
+        <v>609356</v>
       </c>
       <c r="R32" t="n">
-        <v>7018137</v>
+        <v>7018141</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3953,21 +3960,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3984,10 +3976,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124837429</v>
+        <v>124837331</v>
       </c>
       <c r="B33" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3996,25 +3988,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4024,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609251</v>
+        <v>609236</v>
       </c>
       <c r="R33" t="n">
-        <v>7018311</v>
+        <v>7018288</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4086,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124836351</v>
+        <v>124838913</v>
       </c>
       <c r="B34" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4098,25 +4090,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4126,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609330</v>
+        <v>609144</v>
       </c>
       <c r="R34" t="n">
-        <v>7018199</v>
+        <v>7018039</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4188,7 +4180,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124839307</v>
+        <v>124837429</v>
       </c>
       <c r="B35" t="n">
         <v>91299</v>
@@ -4228,10 +4220,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609077</v>
+        <v>609251</v>
       </c>
       <c r="R35" t="n">
-        <v>7018074</v>
+        <v>7018311</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4290,10 +4282,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124837151</v>
+        <v>124839525</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4302,25 +4294,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4322,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609253</v>
+        <v>609068</v>
       </c>
       <c r="R36" t="n">
-        <v>7018298</v>
+        <v>7018108</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4392,7 +4384,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124838979</v>
+        <v>124836709</v>
       </c>
       <c r="B37" t="n">
         <v>91299</v>
@@ -4432,10 +4424,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609132</v>
+        <v>609251</v>
       </c>
       <c r="R37" t="n">
-        <v>7018018</v>
+        <v>7018241</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,10 +4486,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124839318</v>
+        <v>124841439</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,38 +4498,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609091</v>
+        <v>609243</v>
       </c>
       <c r="R38" t="n">
-        <v>7018078</v>
+        <v>7017992</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124835873</v>
+        <v>124838762</v>
       </c>
       <c r="B39" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4612,34 +4608,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609372</v>
+        <v>609202</v>
       </c>
       <c r="R39" t="n">
-        <v>7018137</v>
+        <v>7018017</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124837411</v>
+        <v>124841120</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609251</v>
+        <v>609178</v>
       </c>
       <c r="R6" t="n">
-        <v>7018311</v>
+        <v>7017968</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124836351</v>
+        <v>124837331</v>
       </c>
       <c r="B7" t="n">
         <v>91361</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609330</v>
+        <v>609236</v>
       </c>
       <c r="R7" t="n">
-        <v>7018199</v>
+        <v>7018288</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124840461</v>
+        <v>124837159</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609114</v>
+        <v>609248</v>
       </c>
       <c r="R8" t="n">
-        <v>7018022</v>
+        <v>7018303</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124836147</v>
+        <v>124839525</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,25 +1517,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609334</v>
+        <v>609068</v>
       </c>
       <c r="R9" t="n">
-        <v>7018163</v>
+        <v>7018108</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124841153</v>
+        <v>124841283</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,38 +1619,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609180</v>
+        <v>609215</v>
       </c>
       <c r="R10" t="n">
-        <v>7017969</v>
+        <v>7017959</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124841120</v>
+        <v>124838913</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609178</v>
+        <v>609144</v>
       </c>
       <c r="R11" t="n">
-        <v>7017968</v>
+        <v>7018039</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124836321</v>
+        <v>124836147</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609324</v>
+        <v>609334</v>
       </c>
       <c r="R12" t="n">
-        <v>7018195</v>
+        <v>7018163</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836828</v>
+        <v>124836317</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609243</v>
+        <v>609320</v>
       </c>
       <c r="R13" t="n">
-        <v>7018223</v>
+        <v>7018199</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124836811</v>
+        <v>124838903</v>
       </c>
       <c r="B14" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609241</v>
+        <v>609168</v>
       </c>
       <c r="R14" t="n">
-        <v>7018250</v>
+        <v>7018021</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124837151</v>
+        <v>124837411</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,21 +2137,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609253</v>
+        <v>609251</v>
       </c>
       <c r="R15" t="n">
-        <v>7018298</v>
+        <v>7018311</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124837159</v>
+        <v>124839286</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,21 +2239,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609248</v>
+        <v>609042</v>
       </c>
       <c r="R16" t="n">
-        <v>7018303</v>
+        <v>7018085</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,7 +2325,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124838903</v>
+        <v>124836321</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2361,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609168</v>
+        <v>609324</v>
       </c>
       <c r="R17" t="n">
-        <v>7018021</v>
+        <v>7018195</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124835707</v>
+        <v>124835873</v>
       </c>
       <c r="B18" t="n">
-        <v>91413</v>
+        <v>91673</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,25 +2439,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4217</v>
+        <v>898</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,7 +2467,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609360</v>
+        <v>609372</v>
       </c>
       <c r="R18" t="n">
         <v>7018137</v>
@@ -2509,21 +2513,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2540,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124835668</v>
+        <v>124836692</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2552,25 +2541,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2580,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609359</v>
+        <v>609259</v>
       </c>
       <c r="R19" t="n">
-        <v>7018158</v>
+        <v>7018252</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2642,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124839286</v>
+        <v>124837340</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,25 +2643,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2682,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609042</v>
+        <v>609241</v>
       </c>
       <c r="R20" t="n">
-        <v>7018085</v>
+        <v>7018298</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2744,7 +2733,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124836317</v>
+        <v>124839307</v>
       </c>
       <c r="B21" t="n">
         <v>91299</v>
@@ -2784,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609320</v>
+        <v>609077</v>
       </c>
       <c r="R21" t="n">
-        <v>7018199</v>
+        <v>7018074</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2846,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124839307</v>
+        <v>124835707</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>91413</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2858,25 +2847,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>4217</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609077</v>
+        <v>609360</v>
       </c>
       <c r="R22" t="n">
-        <v>7018074</v>
+        <v>7018137</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2932,6 +2921,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2948,7 +2952,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124839318</v>
+        <v>124835740</v>
       </c>
       <c r="B23" t="n">
         <v>91012</v>
@@ -2988,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609091</v>
+        <v>609356</v>
       </c>
       <c r="R23" t="n">
-        <v>7018078</v>
+        <v>7018141</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3050,7 +3054,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124841283</v>
+        <v>124841439</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3085,7 +3089,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3094,10 +3098,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609215</v>
+        <v>609243</v>
       </c>
       <c r="R24" t="n">
-        <v>7017959</v>
+        <v>7017992</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3156,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124840385</v>
+        <v>124836351</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,38 +3176,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609100</v>
+        <v>609330</v>
       </c>
       <c r="R25" t="n">
-        <v>7018053</v>
+        <v>7018199</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124837223</v>
+        <v>124839318</v>
       </c>
       <c r="B26" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3278,21 +3278,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609229</v>
+        <v>609091</v>
       </c>
       <c r="R26" t="n">
-        <v>7018310</v>
+        <v>7018078</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124836744</v>
+        <v>124837429</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609243</v>
+        <v>609251</v>
       </c>
       <c r="R27" t="n">
-        <v>7018254</v>
+        <v>7018311</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124835873</v>
+        <v>124836709</v>
       </c>
       <c r="B28" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,25 +3478,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609372</v>
+        <v>609251</v>
       </c>
       <c r="R28" t="n">
-        <v>7018137</v>
+        <v>7018241</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124837340</v>
+        <v>124836811</v>
       </c>
       <c r="B29" t="n">
-        <v>90977</v>
+        <v>91361</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3580,25 +3580,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3611,7 +3611,7 @@
         <v>609241</v>
       </c>
       <c r="R29" t="n">
-        <v>7018298</v>
+        <v>7018250</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838979</v>
+        <v>124837223</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609132</v>
+        <v>609229</v>
       </c>
       <c r="R30" t="n">
-        <v>7018018</v>
+        <v>7018310</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124836692</v>
+        <v>124840385</v>
       </c>
       <c r="B31" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,38 +3784,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609259</v>
+        <v>609100</v>
       </c>
       <c r="R31" t="n">
-        <v>7018252</v>
+        <v>7018053</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3874,10 +3878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124835740</v>
+        <v>124840461</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3890,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609356</v>
+        <v>609114</v>
       </c>
       <c r="R32" t="n">
-        <v>7018141</v>
+        <v>7018022</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3976,10 +3980,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124837331</v>
+        <v>124838979</v>
       </c>
       <c r="B33" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,25 +3992,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +4020,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609236</v>
+        <v>609132</v>
       </c>
       <c r="R33" t="n">
-        <v>7018288</v>
+        <v>7018018</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4078,7 +4082,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124838913</v>
+        <v>124841153</v>
       </c>
       <c r="B34" t="n">
         <v>91299</v>
@@ -4118,10 +4122,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609144</v>
+        <v>609180</v>
       </c>
       <c r="R34" t="n">
-        <v>7018039</v>
+        <v>7017969</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4180,7 +4184,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124837429</v>
+        <v>124835668</v>
       </c>
       <c r="B35" t="n">
         <v>91299</v>
@@ -4220,10 +4224,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609251</v>
+        <v>609359</v>
       </c>
       <c r="R35" t="n">
-        <v>7018311</v>
+        <v>7018158</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4282,10 +4286,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124839525</v>
+        <v>124836828</v>
       </c>
       <c r="B36" t="n">
-        <v>91673</v>
+        <v>90962</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,25 +4298,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>898</v>
+        <v>112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4322,10 +4326,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609068</v>
+        <v>609243</v>
       </c>
       <c r="R36" t="n">
-        <v>7018108</v>
+        <v>7018223</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4384,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124836709</v>
+        <v>124836744</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4400,21 +4404,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4424,10 +4428,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R37" t="n">
-        <v>7018241</v>
+        <v>7018254</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4486,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124841439</v>
+        <v>124837151</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4498,42 +4502,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609243</v>
+        <v>609253</v>
       </c>
       <c r="R38" t="n">
-        <v>7017992</v>
+        <v>7018298</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124835740</v>
+        <v>124841439</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,38 +2964,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609356</v>
+        <v>609243</v>
       </c>
       <c r="R23" t="n">
-        <v>7018141</v>
+        <v>7017992</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3054,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124841439</v>
+        <v>124835740</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3066,42 +3070,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609243</v>
+        <v>609356</v>
       </c>
       <c r="R24" t="n">
-        <v>7017992</v>
+        <v>7018141</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124837151</v>
+        <v>124838762</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4502,38 +4502,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609253</v>
+        <v>609202</v>
       </c>
       <c r="R38" t="n">
-        <v>7018298</v>
+        <v>7018017</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4592,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124838762</v>
+        <v>124837151</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4604,42 +4608,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609202</v>
+        <v>609253</v>
       </c>
       <c r="R39" t="n">
-        <v>7018017</v>
+        <v>7018298</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124841120</v>
+        <v>124836321</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609178</v>
+        <v>609324</v>
       </c>
       <c r="R6" t="n">
-        <v>7017968</v>
+        <v>7018195</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124837331</v>
+        <v>124839286</v>
       </c>
       <c r="B7" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,25 +1313,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609236</v>
+        <v>609042</v>
       </c>
       <c r="R7" t="n">
-        <v>7018288</v>
+        <v>7018085</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124837159</v>
+        <v>124837429</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609248</v>
+        <v>609251</v>
       </c>
       <c r="R8" t="n">
-        <v>7018303</v>
+        <v>7018311</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124839525</v>
+        <v>124837331</v>
       </c>
       <c r="B9" t="n">
-        <v>91673</v>
+        <v>91361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609068</v>
+        <v>609236</v>
       </c>
       <c r="R9" t="n">
-        <v>7018108</v>
+        <v>7018288</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124841283</v>
+        <v>124836351</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,38 +1623,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609215</v>
+        <v>609330</v>
       </c>
       <c r="R10" t="n">
-        <v>7017959</v>
+        <v>7018199</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1713,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124838913</v>
+        <v>124835707</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91413</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>4217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609144</v>
+        <v>609360</v>
       </c>
       <c r="R11" t="n">
-        <v>7018039</v>
+        <v>7018137</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1799,6 +1795,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1815,7 +1826,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124836147</v>
+        <v>124838913</v>
       </c>
       <c r="B12" t="n">
         <v>91299</v>
@@ -1855,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609334</v>
+        <v>609144</v>
       </c>
       <c r="R12" t="n">
-        <v>7018163</v>
+        <v>7018039</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1917,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836317</v>
+        <v>124836811</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1940,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609320</v>
+        <v>609241</v>
       </c>
       <c r="R13" t="n">
-        <v>7018199</v>
+        <v>7018250</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2019,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838903</v>
+        <v>124839318</v>
       </c>
       <c r="B14" t="n">
         <v>91012</v>
@@ -2059,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609168</v>
+        <v>609091</v>
       </c>
       <c r="R14" t="n">
-        <v>7018021</v>
+        <v>7018078</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124837411</v>
+        <v>124841439</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,38 +2144,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R15" t="n">
-        <v>7018311</v>
+        <v>7017992</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2223,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124839286</v>
+        <v>124837159</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,21 +2254,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2263,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609042</v>
+        <v>609248</v>
       </c>
       <c r="R16" t="n">
-        <v>7018085</v>
+        <v>7018303</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2325,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124836321</v>
+        <v>124839307</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,21 +2356,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2365,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609324</v>
+        <v>609077</v>
       </c>
       <c r="R17" t="n">
-        <v>7018195</v>
+        <v>7018074</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2427,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124835873</v>
+        <v>124836317</v>
       </c>
       <c r="B18" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,25 +2454,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609372</v>
+        <v>609320</v>
       </c>
       <c r="R18" t="n">
-        <v>7018137</v>
+        <v>7018199</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2529,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124836692</v>
+        <v>124835740</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,25 +2556,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609259</v>
+        <v>609356</v>
       </c>
       <c r="R19" t="n">
-        <v>7018252</v>
+        <v>7018141</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2631,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124837340</v>
+        <v>124836828</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>90962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,25 +2658,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609241</v>
+        <v>609243</v>
       </c>
       <c r="R20" t="n">
-        <v>7018298</v>
+        <v>7018223</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2733,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124839307</v>
+        <v>124835873</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>91673</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,25 +2760,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609077</v>
+        <v>609372</v>
       </c>
       <c r="R21" t="n">
-        <v>7018074</v>
+        <v>7018137</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,10 +2850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124835707</v>
+        <v>124840461</v>
       </c>
       <c r="B22" t="n">
-        <v>91413</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,25 +2862,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2875,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609360</v>
+        <v>609114</v>
       </c>
       <c r="R22" t="n">
-        <v>7018137</v>
+        <v>7018022</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2921,21 +2936,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124841439</v>
+        <v>124838903</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,42 +2964,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609243</v>
+        <v>609168</v>
       </c>
       <c r="R23" t="n">
-        <v>7017992</v>
+        <v>7018021</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3058,10 +3054,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124835740</v>
+        <v>124836692</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3070,25 +3066,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3098,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609356</v>
+        <v>609259</v>
       </c>
       <c r="R24" t="n">
-        <v>7018141</v>
+        <v>7018252</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3160,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124836351</v>
+        <v>124837151</v>
       </c>
       <c r="B25" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,25 +3168,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609330</v>
+        <v>609253</v>
       </c>
       <c r="R25" t="n">
-        <v>7018199</v>
+        <v>7018298</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3262,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124839318</v>
+        <v>124839525</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,25 +3270,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3302,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609091</v>
+        <v>609068</v>
       </c>
       <c r="R26" t="n">
-        <v>7018078</v>
+        <v>7018108</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3364,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124837429</v>
+        <v>124838979</v>
       </c>
       <c r="B27" t="n">
         <v>91299</v>
@@ -3404,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609251</v>
+        <v>609132</v>
       </c>
       <c r="R27" t="n">
-        <v>7018311</v>
+        <v>7018018</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3466,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124836709</v>
+        <v>124837340</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,25 +3474,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609251</v>
+        <v>609241</v>
       </c>
       <c r="R28" t="n">
-        <v>7018241</v>
+        <v>7018298</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3568,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124836811</v>
+        <v>124836147</v>
       </c>
       <c r="B29" t="n">
-        <v>91361</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3580,25 +3576,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609241</v>
+        <v>609334</v>
       </c>
       <c r="R29" t="n">
-        <v>7018250</v>
+        <v>7018163</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3670,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124837223</v>
+        <v>124840385</v>
       </c>
       <c r="B30" t="n">
-        <v>91026</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,38 +3678,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609229</v>
+        <v>609100</v>
       </c>
       <c r="R30" t="n">
-        <v>7018310</v>
+        <v>7018053</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124840385</v>
+        <v>124838762</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609100</v>
+        <v>609202</v>
       </c>
       <c r="R31" t="n">
-        <v>7018053</v>
+        <v>7018017</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124840461</v>
+        <v>124836744</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3894,21 +3894,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609114</v>
+        <v>609243</v>
       </c>
       <c r="R32" t="n">
-        <v>7018022</v>
+        <v>7018254</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124838979</v>
+        <v>124836709</v>
       </c>
       <c r="B33" t="n">
         <v>91299</v>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609132</v>
+        <v>609251</v>
       </c>
       <c r="R33" t="n">
-        <v>7018018</v>
+        <v>7018241</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124841153</v>
+        <v>124837223</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609180</v>
+        <v>609229</v>
       </c>
       <c r="R34" t="n">
-        <v>7017969</v>
+        <v>7018310</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124836828</v>
+        <v>124841153</v>
       </c>
       <c r="B36" t="n">
-        <v>90962</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4302,21 +4302,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609243</v>
+        <v>609180</v>
       </c>
       <c r="R36" t="n">
-        <v>7018223</v>
+        <v>7017969</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124836744</v>
+        <v>124841120</v>
       </c>
       <c r="B37" t="n">
         <v>91012</v>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609243</v>
+        <v>609178</v>
       </c>
       <c r="R37" t="n">
-        <v>7018254</v>
+        <v>7017968</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124838762</v>
+        <v>124837411</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4502,42 +4502,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609202</v>
+        <v>609251</v>
       </c>
       <c r="R38" t="n">
-        <v>7018017</v>
+        <v>7018311</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124837151</v>
+        <v>124841283</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,38 +4604,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609253</v>
+        <v>609215</v>
       </c>
       <c r="R39" t="n">
-        <v>7018298</v>
+        <v>7017959</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124836321</v>
+        <v>124837331</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609324</v>
+        <v>609236</v>
       </c>
       <c r="R6" t="n">
-        <v>7018195</v>
+        <v>7018288</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124839286</v>
+        <v>124836321</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609042</v>
+        <v>609324</v>
       </c>
       <c r="R7" t="n">
-        <v>7018085</v>
+        <v>7018195</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124837429</v>
+        <v>124837411</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124837331</v>
+        <v>124835740</v>
       </c>
       <c r="B9" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,25 +1517,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609236</v>
+        <v>609356</v>
       </c>
       <c r="R9" t="n">
-        <v>7018288</v>
+        <v>7018141</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124836351</v>
+        <v>124836811</v>
       </c>
       <c r="B10" t="n">
         <v>91361</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609330</v>
+        <v>609241</v>
       </c>
       <c r="R10" t="n">
-        <v>7018199</v>
+        <v>7018250</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124835707</v>
+        <v>124837429</v>
       </c>
       <c r="B11" t="n">
-        <v>91413</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609360</v>
+        <v>609251</v>
       </c>
       <c r="R11" t="n">
-        <v>7018137</v>
+        <v>7018311</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1795,21 +1795,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1826,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124838913</v>
+        <v>124837159</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,21 +1827,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609144</v>
+        <v>609248</v>
       </c>
       <c r="R12" t="n">
-        <v>7018039</v>
+        <v>7018303</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1928,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836811</v>
+        <v>124839525</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>91673</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>898</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1968,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609241</v>
+        <v>609068</v>
       </c>
       <c r="R13" t="n">
-        <v>7018250</v>
+        <v>7018108</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2030,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124839318</v>
+        <v>124838913</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,21 +2031,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2070,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609091</v>
+        <v>609144</v>
       </c>
       <c r="R14" t="n">
-        <v>7018078</v>
+        <v>7018039</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2132,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124841439</v>
+        <v>124841120</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,42 +2129,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609243</v>
+        <v>609178</v>
       </c>
       <c r="R15" t="n">
-        <v>7017992</v>
+        <v>7017968</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2238,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124837159</v>
+        <v>124841153</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609248</v>
+        <v>609180</v>
       </c>
       <c r="R16" t="n">
-        <v>7018303</v>
+        <v>7017969</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2340,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124839307</v>
+        <v>124838903</v>
       </c>
       <c r="B17" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,21 +2337,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609077</v>
+        <v>609168</v>
       </c>
       <c r="R17" t="n">
-        <v>7018074</v>
+        <v>7018021</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2442,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124836317</v>
+        <v>124840385</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,38 +2435,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609320</v>
+        <v>609100</v>
       </c>
       <c r="R18" t="n">
-        <v>7018199</v>
+        <v>7018053</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2544,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124835740</v>
+        <v>124837151</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,21 +2545,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2584,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609356</v>
+        <v>609253</v>
       </c>
       <c r="R19" t="n">
-        <v>7018141</v>
+        <v>7018298</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2646,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124836828</v>
+        <v>124839307</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2662,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2686,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609243</v>
+        <v>609077</v>
       </c>
       <c r="R20" t="n">
-        <v>7018223</v>
+        <v>7018074</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2748,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124835873</v>
+        <v>124838762</v>
       </c>
       <c r="B21" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2764,34 +2749,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609372</v>
+        <v>609202</v>
       </c>
       <c r="R21" t="n">
-        <v>7018137</v>
+        <v>7018017</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2850,7 +2839,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124840461</v>
+        <v>124836709</v>
       </c>
       <c r="B22" t="n">
         <v>91299</v>
@@ -2890,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609114</v>
+        <v>609251</v>
       </c>
       <c r="R22" t="n">
-        <v>7018022</v>
+        <v>7018241</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2952,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124838903</v>
+        <v>124836317</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,21 +2957,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609168</v>
+        <v>609320</v>
       </c>
       <c r="R23" t="n">
-        <v>7018021</v>
+        <v>7018199</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3054,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124836692</v>
+        <v>124841439</v>
       </c>
       <c r="B24" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3066,38 +3055,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609259</v>
+        <v>609243</v>
       </c>
       <c r="R24" t="n">
-        <v>7018252</v>
+        <v>7017992</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3156,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124837151</v>
+        <v>124840461</v>
       </c>
       <c r="B25" t="n">
         <v>91299</v>
@@ -3196,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609253</v>
+        <v>609114</v>
       </c>
       <c r="R25" t="n">
-        <v>7018298</v>
+        <v>7018022</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3258,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124839525</v>
+        <v>124835668</v>
       </c>
       <c r="B26" t="n">
-        <v>91673</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3270,25 +3263,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3298,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609068</v>
+        <v>609359</v>
       </c>
       <c r="R26" t="n">
-        <v>7018108</v>
+        <v>7018158</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3360,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124838979</v>
+        <v>124837340</v>
       </c>
       <c r="B27" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,25 +3365,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609132</v>
+        <v>609241</v>
       </c>
       <c r="R27" t="n">
-        <v>7018018</v>
+        <v>7018298</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3462,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124837340</v>
+        <v>124835873</v>
       </c>
       <c r="B28" t="n">
-        <v>90977</v>
+        <v>91673</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3474,25 +3467,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3502,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609241</v>
+        <v>609372</v>
       </c>
       <c r="R28" t="n">
-        <v>7018298</v>
+        <v>7018137</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3564,10 +3557,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124836147</v>
+        <v>124841283</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3576,38 +3569,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609334</v>
+        <v>609215</v>
       </c>
       <c r="R29" t="n">
-        <v>7018163</v>
+        <v>7017959</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3666,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124840385</v>
+        <v>124836351</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,38 +3679,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609100</v>
+        <v>609330</v>
       </c>
       <c r="R30" t="n">
-        <v>7018053</v>
+        <v>7018199</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3772,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124838762</v>
+        <v>124836828</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>90962</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,42 +3777,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609202</v>
+        <v>609243</v>
       </c>
       <c r="R31" t="n">
-        <v>7018017</v>
+        <v>7018223</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3878,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124836744</v>
+        <v>124839286</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3894,21 +3883,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3918,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609243</v>
+        <v>609042</v>
       </c>
       <c r="R32" t="n">
-        <v>7018254</v>
+        <v>7018085</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3980,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124836709</v>
+        <v>124836692</v>
       </c>
       <c r="B33" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3992,25 +3981,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4020,10 +4009,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609251</v>
+        <v>609259</v>
       </c>
       <c r="R33" t="n">
-        <v>7018241</v>
+        <v>7018252</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4082,10 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124837223</v>
+        <v>124835707</v>
       </c>
       <c r="B34" t="n">
-        <v>91026</v>
+        <v>91413</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4094,25 +4083,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>4217</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4122,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609229</v>
+        <v>609360</v>
       </c>
       <c r="R34" t="n">
-        <v>7018310</v>
+        <v>7018137</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4168,6 +4157,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4184,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124835668</v>
+        <v>124839318</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4200,21 +4204,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4224,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609359</v>
+        <v>609091</v>
       </c>
       <c r="R35" t="n">
-        <v>7018158</v>
+        <v>7018078</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4286,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124841153</v>
+        <v>124837223</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4302,21 +4306,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4326,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609180</v>
+        <v>609229</v>
       </c>
       <c r="R36" t="n">
-        <v>7017969</v>
+        <v>7018310</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4388,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124841120</v>
+        <v>124836147</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4404,21 +4408,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4428,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609178</v>
+        <v>609334</v>
       </c>
       <c r="R37" t="n">
-        <v>7017968</v>
+        <v>7018163</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4490,7 +4494,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124837411</v>
+        <v>124836744</v>
       </c>
       <c r="B38" t="n">
         <v>91012</v>
@@ -4530,10 +4534,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R38" t="n">
-        <v>7018311</v>
+        <v>7018254</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4592,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124841283</v>
+        <v>124838979</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4604,42 +4608,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609215</v>
+        <v>609132</v>
       </c>
       <c r="R39" t="n">
-        <v>7017959</v>
+        <v>7018018</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124837331</v>
+        <v>124837429</v>
       </c>
       <c r="B6" t="n">
-        <v>91361</v>
+        <v>91459</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609236</v>
+        <v>609251</v>
       </c>
       <c r="R6" t="n">
-        <v>7018288</v>
+        <v>7018311</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124836321</v>
+        <v>124839307</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91459</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609324</v>
+        <v>609077</v>
       </c>
       <c r="R7" t="n">
-        <v>7018195</v>
+        <v>7018074</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124837411</v>
+        <v>124836147</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91459</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609251</v>
+        <v>609334</v>
       </c>
       <c r="R8" t="n">
-        <v>7018311</v>
+        <v>7018163</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124835740</v>
+        <v>124837331</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91521</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,25 +1517,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609356</v>
+        <v>609236</v>
       </c>
       <c r="R9" t="n">
-        <v>7018141</v>
+        <v>7018288</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124836811</v>
+        <v>124841153</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>91459</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,25 +1619,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609241</v>
+        <v>609180</v>
       </c>
       <c r="R10" t="n">
-        <v>7018250</v>
+        <v>7017969</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124837429</v>
+        <v>124841439</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,38 +1721,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R11" t="n">
-        <v>7018311</v>
+        <v>7017992</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124837159</v>
+        <v>124836321</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609248</v>
+        <v>609324</v>
       </c>
       <c r="R12" t="n">
-        <v>7018303</v>
+        <v>7018195</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124839525</v>
+        <v>124837340</v>
       </c>
       <c r="B13" t="n">
-        <v>91673</v>
+        <v>91131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,25 +1929,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609068</v>
+        <v>609241</v>
       </c>
       <c r="R13" t="n">
-        <v>7018108</v>
+        <v>7018298</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838913</v>
+        <v>124838979</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609144</v>
+        <v>609132</v>
       </c>
       <c r="R14" t="n">
-        <v>7018039</v>
+        <v>7018018</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124841120</v>
+        <v>124837159</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609178</v>
+        <v>609248</v>
       </c>
       <c r="R15" t="n">
-        <v>7017968</v>
+        <v>7018303</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124841153</v>
+        <v>124837151</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609180</v>
+        <v>609253</v>
       </c>
       <c r="R16" t="n">
-        <v>7017969</v>
+        <v>7018298</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124838903</v>
+        <v>124837411</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609168</v>
+        <v>609251</v>
       </c>
       <c r="R17" t="n">
-        <v>7018021</v>
+        <v>7018311</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124840385</v>
+        <v>124836811</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91521</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,38 +2443,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609100</v>
+        <v>609241</v>
       </c>
       <c r="R18" t="n">
-        <v>7018053</v>
+        <v>7018250</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124837151</v>
+        <v>124836709</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609253</v>
+        <v>609251</v>
       </c>
       <c r="R19" t="n">
-        <v>7018298</v>
+        <v>7018241</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124839307</v>
+        <v>124836317</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609077</v>
+        <v>609320</v>
       </c>
       <c r="R20" t="n">
-        <v>7018074</v>
+        <v>7018199</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124838762</v>
+        <v>124835707</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,42 +2745,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609202</v>
+        <v>609360</v>
       </c>
       <c r="R21" t="n">
-        <v>7018017</v>
+        <v>7018137</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2823,6 +2819,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2839,10 +2850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124836709</v>
+        <v>124841283</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,38 +2862,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609251</v>
+        <v>609215</v>
       </c>
       <c r="R22" t="n">
-        <v>7018241</v>
+        <v>7017959</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2941,10 +2956,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124836317</v>
+        <v>124839318</v>
       </c>
       <c r="B23" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,21 +2972,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609320</v>
+        <v>609091</v>
       </c>
       <c r="R23" t="n">
-        <v>7018199</v>
+        <v>7018078</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3043,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124841439</v>
+        <v>124836692</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,42 +3070,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609243</v>
+        <v>609259</v>
       </c>
       <c r="R24" t="n">
-        <v>7017992</v>
+        <v>7018252</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3149,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124840461</v>
+        <v>124838903</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,21 +3176,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609114</v>
+        <v>609168</v>
       </c>
       <c r="R25" t="n">
-        <v>7018022</v>
+        <v>7018021</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3251,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124835668</v>
+        <v>124835740</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,21 +3278,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3291,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609359</v>
+        <v>609356</v>
       </c>
       <c r="R26" t="n">
-        <v>7018158</v>
+        <v>7018141</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3353,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124837340</v>
+        <v>124836744</v>
       </c>
       <c r="B27" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,25 +3376,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3393,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609241</v>
+        <v>609243</v>
       </c>
       <c r="R27" t="n">
-        <v>7018298</v>
+        <v>7018254</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3458,7 +3469,7 @@
         <v>124835873</v>
       </c>
       <c r="B28" t="n">
-        <v>91673</v>
+        <v>91833</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3557,10 +3568,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124841283</v>
+        <v>124839286</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,42 +3580,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609215</v>
+        <v>609042</v>
       </c>
       <c r="R29" t="n">
-        <v>7017959</v>
+        <v>7018085</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3663,10 +3670,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124836351</v>
+        <v>124840461</v>
       </c>
       <c r="B30" t="n">
-        <v>91361</v>
+        <v>91459</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3675,25 +3682,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609330</v>
+        <v>609114</v>
       </c>
       <c r="R30" t="n">
-        <v>7018199</v>
+        <v>7018022</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3765,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124836828</v>
+        <v>124837223</v>
       </c>
       <c r="B31" t="n">
-        <v>90962</v>
+        <v>91180</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3781,21 +3788,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609243</v>
+        <v>609229</v>
       </c>
       <c r="R31" t="n">
-        <v>7018223</v>
+        <v>7018310</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3867,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124839286</v>
+        <v>124836351</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>91521</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3879,25 +3886,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609042</v>
+        <v>609330</v>
       </c>
       <c r="R32" t="n">
-        <v>7018085</v>
+        <v>7018199</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3969,10 +3976,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124836692</v>
+        <v>124841120</v>
       </c>
       <c r="B33" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3981,25 +3988,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4009,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609259</v>
+        <v>609178</v>
       </c>
       <c r="R33" t="n">
-        <v>7018252</v>
+        <v>7017968</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4071,10 +4078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124835707</v>
+        <v>124840385</v>
       </c>
       <c r="B34" t="n">
-        <v>91413</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4083,38 +4090,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609360</v>
+        <v>609100</v>
       </c>
       <c r="R34" t="n">
-        <v>7018137</v>
+        <v>7018053</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4157,21 +4168,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4188,10 +4184,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124839318</v>
+        <v>124839525</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>91833</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4200,25 +4196,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4224,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609091</v>
+        <v>609068</v>
       </c>
       <c r="R35" t="n">
-        <v>7018078</v>
+        <v>7018108</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4290,10 +4286,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124837223</v>
+        <v>124835668</v>
       </c>
       <c r="B36" t="n">
-        <v>91026</v>
+        <v>91459</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4306,21 +4302,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4326,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609229</v>
+        <v>609359</v>
       </c>
       <c r="R36" t="n">
-        <v>7018310</v>
+        <v>7018158</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4392,10 +4388,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124836147</v>
+        <v>124836828</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91116</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4408,21 +4404,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4432,10 +4428,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609334</v>
+        <v>609243</v>
       </c>
       <c r="R37" t="n">
-        <v>7018163</v>
+        <v>7018223</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,10 +4490,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124836744</v>
+        <v>124838762</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,38 +4502,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609243</v>
+        <v>609202</v>
       </c>
       <c r="R38" t="n">
-        <v>7018254</v>
+        <v>7018017</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124838979</v>
+        <v>124838913</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609132</v>
+        <v>609144</v>
       </c>
       <c r="R39" t="n">
-        <v>7018018</v>
+        <v>7018039</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124836317</v>
+        <v>124835707</v>
       </c>
       <c r="B20" t="n">
-        <v>91459</v>
+        <v>91573</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,25 +2643,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>4217</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609320</v>
+        <v>609360</v>
       </c>
       <c r="R20" t="n">
-        <v>7018199</v>
+        <v>7018137</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2717,6 +2717,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2733,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124835707</v>
+        <v>124836317</v>
       </c>
       <c r="B21" t="n">
-        <v>91573</v>
+        <v>91459</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,25 +2760,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609360</v>
+        <v>609320</v>
       </c>
       <c r="R21" t="n">
-        <v>7018137</v>
+        <v>7018199</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2819,21 +2834,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2850,10 +2850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124841283</v>
+        <v>124839318</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,42 +2862,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609215</v>
+        <v>609091</v>
       </c>
       <c r="R22" t="n">
-        <v>7017959</v>
+        <v>7018078</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2956,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124839318</v>
+        <v>124836692</v>
       </c>
       <c r="B23" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,25 +2964,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2996,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609091</v>
+        <v>609259</v>
       </c>
       <c r="R23" t="n">
-        <v>7018078</v>
+        <v>7018252</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3058,10 +3054,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124836692</v>
+        <v>124838903</v>
       </c>
       <c r="B24" t="n">
-        <v>91131</v>
+        <v>91166</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3070,25 +3066,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3098,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609259</v>
+        <v>609168</v>
       </c>
       <c r="R24" t="n">
-        <v>7018252</v>
+        <v>7018021</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3160,7 +3156,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124838903</v>
+        <v>124835740</v>
       </c>
       <c r="B25" t="n">
         <v>91166</v>
@@ -3200,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609168</v>
+        <v>609356</v>
       </c>
       <c r="R25" t="n">
-        <v>7018021</v>
+        <v>7018141</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3262,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124835740</v>
+        <v>124841283</v>
       </c>
       <c r="B26" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,38 +3270,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609356</v>
+        <v>609215</v>
       </c>
       <c r="R26" t="n">
-        <v>7018141</v>
+        <v>7017959</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124839525</v>
+        <v>124838762</v>
       </c>
       <c r="B35" t="n">
-        <v>91833</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4200,34 +4200,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609068</v>
+        <v>609202</v>
       </c>
       <c r="R35" t="n">
-        <v>7018108</v>
+        <v>7018017</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4286,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124835668</v>
+        <v>124839525</v>
       </c>
       <c r="B36" t="n">
-        <v>91459</v>
+        <v>91833</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4298,25 +4302,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4326,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609359</v>
+        <v>609068</v>
       </c>
       <c r="R36" t="n">
-        <v>7018158</v>
+        <v>7018108</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4388,10 +4392,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124836828</v>
+        <v>124835668</v>
       </c>
       <c r="B37" t="n">
-        <v>91116</v>
+        <v>91459</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4404,21 +4408,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4428,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609243</v>
+        <v>609359</v>
       </c>
       <c r="R37" t="n">
-        <v>7018223</v>
+        <v>7018158</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4490,10 +4494,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124838762</v>
+        <v>124836828</v>
       </c>
       <c r="B38" t="n">
-        <v>98269</v>
+        <v>91116</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4502,42 +4506,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609202</v>
+        <v>609243</v>
       </c>
       <c r="R38" t="n">
-        <v>7018017</v>
+        <v>7018223</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,7 +1199,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124837429</v>
+        <v>124836317</v>
       </c>
       <c r="B6" t="n">
         <v>91459</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609251</v>
+        <v>609320</v>
       </c>
       <c r="R6" t="n">
-        <v>7018311</v>
+        <v>7018199</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124839307</v>
+        <v>124837151</v>
       </c>
       <c r="B7" t="n">
         <v>91459</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609077</v>
+        <v>609253</v>
       </c>
       <c r="R7" t="n">
-        <v>7018074</v>
+        <v>7018298</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,7 +1403,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124836147</v>
+        <v>124837429</v>
       </c>
       <c r="B8" t="n">
         <v>91459</v>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609334</v>
+        <v>609251</v>
       </c>
       <c r="R8" t="n">
-        <v>7018163</v>
+        <v>7018311</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124837331</v>
+        <v>124841153</v>
       </c>
       <c r="B9" t="n">
-        <v>91521</v>
+        <v>91459</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,25 +1517,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609236</v>
+        <v>609180</v>
       </c>
       <c r="R9" t="n">
-        <v>7018288</v>
+        <v>7017969</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124841153</v>
+        <v>124838903</v>
       </c>
       <c r="B10" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,21 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609180</v>
+        <v>609168</v>
       </c>
       <c r="R10" t="n">
-        <v>7017969</v>
+        <v>7018021</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124841439</v>
+        <v>124835668</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,42 +1721,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609243</v>
+        <v>609359</v>
       </c>
       <c r="R11" t="n">
-        <v>7017992</v>
+        <v>7018158</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1815,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124836321</v>
+        <v>124841120</v>
       </c>
       <c r="B12" t="n">
         <v>91166</v>
@@ -1855,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609324</v>
+        <v>609178</v>
       </c>
       <c r="R12" t="n">
-        <v>7018195</v>
+        <v>7017968</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1917,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124837340</v>
+        <v>124836147</v>
       </c>
       <c r="B13" t="n">
-        <v>91131</v>
+        <v>91459</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1925,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609241</v>
+        <v>609334</v>
       </c>
       <c r="R13" t="n">
-        <v>7018298</v>
+        <v>7018163</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2019,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124838979</v>
+        <v>124837159</v>
       </c>
       <c r="B14" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2031,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609132</v>
+        <v>609248</v>
       </c>
       <c r="R14" t="n">
-        <v>7018018</v>
+        <v>7018303</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124837159</v>
+        <v>124836351</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
+        <v>91521</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,25 +2129,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609248</v>
+        <v>609330</v>
       </c>
       <c r="R15" t="n">
-        <v>7018303</v>
+        <v>7018199</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2223,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124837151</v>
+        <v>124836744</v>
       </c>
       <c r="B16" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2263,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609253</v>
+        <v>609243</v>
       </c>
       <c r="R16" t="n">
-        <v>7018298</v>
+        <v>7018254</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2325,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124837411</v>
+        <v>124836828</v>
       </c>
       <c r="B17" t="n">
-        <v>91166</v>
+        <v>91116</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,21 +2337,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2365,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R17" t="n">
-        <v>7018311</v>
+        <v>7018223</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2427,7 +2423,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124836811</v>
+        <v>124837331</v>
       </c>
       <c r="B18" t="n">
         <v>91521</v>
@@ -2467,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609241</v>
+        <v>609236</v>
       </c>
       <c r="R18" t="n">
-        <v>7018250</v>
+        <v>7018288</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2529,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124836709</v>
+        <v>124838762</v>
       </c>
       <c r="B19" t="n">
-        <v>91459</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,38 +2537,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609251</v>
+        <v>609202</v>
       </c>
       <c r="R19" t="n">
-        <v>7018241</v>
+        <v>7018017</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124835707</v>
+        <v>124836709</v>
       </c>
       <c r="B20" t="n">
-        <v>91573</v>
+        <v>91459</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,25 +2643,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609360</v>
+        <v>609251</v>
       </c>
       <c r="R20" t="n">
-        <v>7018137</v>
+        <v>7018241</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2717,21 +2717,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2748,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124836317</v>
+        <v>124835873</v>
       </c>
       <c r="B21" t="n">
-        <v>91459</v>
+        <v>91833</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,25 +2745,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2788,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609320</v>
+        <v>609372</v>
       </c>
       <c r="R21" t="n">
-        <v>7018199</v>
+        <v>7018137</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2850,7 +2835,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124839318</v>
+        <v>124835740</v>
       </c>
       <c r="B22" t="n">
         <v>91166</v>
@@ -2890,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609091</v>
+        <v>609356</v>
       </c>
       <c r="R22" t="n">
-        <v>7018078</v>
+        <v>7018141</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2952,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124836692</v>
+        <v>124841283</v>
       </c>
       <c r="B23" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,38 +2949,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609259</v>
+        <v>609215</v>
       </c>
       <c r="R23" t="n">
-        <v>7018252</v>
+        <v>7017959</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3054,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124838903</v>
+        <v>124835707</v>
       </c>
       <c r="B24" t="n">
-        <v>91166</v>
+        <v>91573</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3066,25 +3055,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3094,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609168</v>
+        <v>609360</v>
       </c>
       <c r="R24" t="n">
-        <v>7018021</v>
+        <v>7018137</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3140,6 +3129,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3156,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124835740</v>
+        <v>124837223</v>
       </c>
       <c r="B25" t="n">
-        <v>91166</v>
+        <v>91180</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,21 +3176,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3196,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609356</v>
+        <v>609229</v>
       </c>
       <c r="R25" t="n">
-        <v>7018141</v>
+        <v>7018310</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3258,7 +3262,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124841283</v>
+        <v>124840385</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
@@ -3302,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609215</v>
+        <v>609100</v>
       </c>
       <c r="R26" t="n">
-        <v>7017959</v>
+        <v>7018053</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3364,10 +3368,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124836744</v>
+        <v>124841439</v>
       </c>
       <c r="B27" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3376,28 +3380,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
@@ -3407,7 +3415,7 @@
         <v>609243</v>
       </c>
       <c r="R27" t="n">
-        <v>7018254</v>
+        <v>7017992</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3466,10 +3474,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124835873</v>
+        <v>124840461</v>
       </c>
       <c r="B28" t="n">
-        <v>91833</v>
+        <v>91459</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,25 +3486,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3514,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609372</v>
+        <v>609114</v>
       </c>
       <c r="R28" t="n">
-        <v>7018137</v>
+        <v>7018022</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3568,7 +3576,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124839286</v>
+        <v>124838913</v>
       </c>
       <c r="B29" t="n">
         <v>91459</v>
@@ -3608,10 +3616,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609042</v>
+        <v>609144</v>
       </c>
       <c r="R29" t="n">
-        <v>7018085</v>
+        <v>7018039</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3670,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124840461</v>
+        <v>124836321</v>
       </c>
       <c r="B30" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3686,21 +3694,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3718,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609114</v>
+        <v>609324</v>
       </c>
       <c r="R30" t="n">
-        <v>7018022</v>
+        <v>7018195</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3772,10 +3780,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124837223</v>
+        <v>124838979</v>
       </c>
       <c r="B31" t="n">
-        <v>91180</v>
+        <v>91459</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,21 +3796,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3812,10 +3820,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609229</v>
+        <v>609132</v>
       </c>
       <c r="R31" t="n">
-        <v>7018310</v>
+        <v>7018018</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3874,10 +3882,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124836351</v>
+        <v>124836692</v>
       </c>
       <c r="B32" t="n">
-        <v>91521</v>
+        <v>91131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,25 +3894,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609330</v>
+        <v>609259</v>
       </c>
       <c r="R32" t="n">
-        <v>7018199</v>
+        <v>7018252</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3976,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124841120</v>
+        <v>124839525</v>
       </c>
       <c r="B33" t="n">
-        <v>91166</v>
+        <v>91833</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,25 +3996,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +4024,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609178</v>
+        <v>609068</v>
       </c>
       <c r="R33" t="n">
-        <v>7017968</v>
+        <v>7018108</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4078,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124840385</v>
+        <v>124839318</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,42 +4098,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609100</v>
+        <v>609091</v>
       </c>
       <c r="R34" t="n">
-        <v>7018053</v>
+        <v>7018078</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4184,10 +4188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124838762</v>
+        <v>124837411</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4196,42 +4200,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609202</v>
+        <v>609251</v>
       </c>
       <c r="R35" t="n">
-        <v>7018017</v>
+        <v>7018311</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124839525</v>
+        <v>124837340</v>
       </c>
       <c r="B36" t="n">
-        <v>91833</v>
+        <v>91131</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4302,25 +4302,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609068</v>
+        <v>609241</v>
       </c>
       <c r="R36" t="n">
-        <v>7018108</v>
+        <v>7018298</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124835668</v>
+        <v>124839307</v>
       </c>
       <c r="B37" t="n">
         <v>91459</v>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609359</v>
+        <v>609077</v>
       </c>
       <c r="R37" t="n">
-        <v>7018158</v>
+        <v>7018074</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124836828</v>
+        <v>124836811</v>
       </c>
       <c r="B38" t="n">
-        <v>91116</v>
+        <v>91521</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4506,25 +4506,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>112</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609243</v>
+        <v>609241</v>
       </c>
       <c r="R38" t="n">
-        <v>7018223</v>
+        <v>7018250</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124838913</v>
+        <v>124839286</v>
       </c>
       <c r="B39" t="n">
         <v>91459</v>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609144</v>
+        <v>609042</v>
       </c>
       <c r="R39" t="n">
-        <v>7018039</v>
+        <v>7018085</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124838903</v>
+        <v>124835668</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,21 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609168</v>
+        <v>609359</v>
       </c>
       <c r="R10" t="n">
-        <v>7018021</v>
+        <v>7018158</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124835668</v>
+        <v>124838903</v>
       </c>
       <c r="B11" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609359</v>
+        <v>609168</v>
       </c>
       <c r="R11" t="n">
-        <v>7018158</v>
+        <v>7018021</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124837223</v>
+        <v>124840385</v>
       </c>
       <c r="B25" t="n">
-        <v>91180</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,38 +3172,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609229</v>
+        <v>609100</v>
       </c>
       <c r="R25" t="n">
-        <v>7018310</v>
+        <v>7018053</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3262,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124840385</v>
+        <v>124837223</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
+        <v>91180</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,42 +3278,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609100</v>
+        <v>609229</v>
       </c>
       <c r="R26" t="n">
-        <v>7018053</v>
+        <v>7018310</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -1199,15 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124836317</v>
+        <v>124836744</v>
       </c>
       <c r="B6" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,21 +1210,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1234,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609320</v>
+        <v>609243</v>
       </c>
       <c r="R6" t="n">
-        <v>7018199</v>
+        <v>7018254</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1301,50 +1296,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124837151</v>
+        <v>124838762</v>
       </c>
       <c r="B7" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609253</v>
+        <v>609202</v>
       </c>
       <c r="R7" t="n">
-        <v>7018298</v>
+        <v>7018017</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,50 +1397,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124837429</v>
+        <v>124841439</v>
       </c>
       <c r="B8" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609251</v>
+        <v>609243</v>
       </c>
       <c r="R8" t="n">
-        <v>7018311</v>
+        <v>7017992</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,15 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124841153</v>
+        <v>124838903</v>
       </c>
       <c r="B9" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,21 +1509,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609180</v>
+        <v>609168</v>
       </c>
       <c r="R9" t="n">
-        <v>7017969</v>
+        <v>7018021</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,16 +1595,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124835668</v>
+        <v>124836317</v>
       </c>
       <c r="B10" t="n">
         <v>91459</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1647,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609359</v>
+        <v>609320</v>
       </c>
       <c r="R10" t="n">
-        <v>7018158</v>
+        <v>7018199</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,37 +1692,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124838903</v>
+        <v>124837340</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609168</v>
+        <v>609241</v>
       </c>
       <c r="R11" t="n">
-        <v>7018021</v>
+        <v>7018298</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,15 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124841120</v>
+        <v>124839286</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1824,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609178</v>
+        <v>609042</v>
       </c>
       <c r="R12" t="n">
-        <v>7017968</v>
+        <v>7018085</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,37 +1886,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124836147</v>
+        <v>124839525</v>
       </c>
       <c r="B13" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609334</v>
+        <v>609068</v>
       </c>
       <c r="R13" t="n">
-        <v>7018163</v>
+        <v>7018108</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,50 +1983,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124837159</v>
+        <v>124841283</v>
       </c>
       <c r="B14" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609248</v>
+        <v>609215</v>
       </c>
       <c r="R14" t="n">
-        <v>7018303</v>
+        <v>7017959</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,37 +2084,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124836351</v>
+        <v>124836709</v>
       </c>
       <c r="B15" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609330</v>
+        <v>609251</v>
       </c>
       <c r="R15" t="n">
-        <v>7018199</v>
+        <v>7018241</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,15 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124836744</v>
+        <v>124837429</v>
       </c>
       <c r="B16" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,21 +2192,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609243</v>
+        <v>609251</v>
       </c>
       <c r="R16" t="n">
-        <v>7018254</v>
+        <v>7018311</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,37 +2278,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124836828</v>
+        <v>124835873</v>
       </c>
       <c r="B17" t="n">
-        <v>91116</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>898</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609243</v>
+        <v>609372</v>
       </c>
       <c r="R17" t="n">
-        <v>7018223</v>
+        <v>7018137</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,37 +2375,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124837331</v>
+        <v>124835668</v>
       </c>
       <c r="B18" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609236</v>
+        <v>609359</v>
       </c>
       <c r="R18" t="n">
-        <v>7018288</v>
+        <v>7018158</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2525,54 +2472,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124838762</v>
+        <v>124837159</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609202</v>
+        <v>609248</v>
       </c>
       <c r="R19" t="n">
-        <v>7018017</v>
+        <v>7018303</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2631,37 +2569,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124836709</v>
+        <v>124836811</v>
       </c>
       <c r="B20" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609251</v>
+        <v>609241</v>
       </c>
       <c r="R20" t="n">
-        <v>7018241</v>
+        <v>7018250</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2733,37 +2666,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124835873</v>
+        <v>124836828</v>
       </c>
       <c r="B21" t="n">
-        <v>91833</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>898</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2773,10 +2701,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>609372</v>
+        <v>609243</v>
       </c>
       <c r="R21" t="n">
-        <v>7018137</v>
+        <v>7018223</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,16 +2763,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124835740</v>
+        <v>124841120</v>
       </c>
       <c r="B22" t="n">
         <v>91166</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2875,10 +2798,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609356</v>
+        <v>609178</v>
       </c>
       <c r="R22" t="n">
-        <v>7018141</v>
+        <v>7017968</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2937,54 +2860,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124841283</v>
+        <v>124836147</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609215</v>
+        <v>609334</v>
       </c>
       <c r="R23" t="n">
-        <v>7017959</v>
+        <v>7018163</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3043,37 +2957,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124835707</v>
+        <v>124841153</v>
       </c>
       <c r="B24" t="n">
-        <v>91573</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +2992,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609360</v>
+        <v>609180</v>
       </c>
       <c r="R24" t="n">
-        <v>7018137</v>
+        <v>7017969</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3129,21 +3038,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3160,54 +3054,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124840385</v>
+        <v>124839318</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609100</v>
+        <v>609091</v>
       </c>
       <c r="R25" t="n">
-        <v>7018053</v>
+        <v>7018078</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3266,15 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124837223</v>
+        <v>124839307</v>
       </c>
       <c r="B26" t="n">
-        <v>91180</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3282,21 +3162,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3306,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609229</v>
+        <v>609077</v>
       </c>
       <c r="R26" t="n">
-        <v>7018310</v>
+        <v>7018074</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3368,54 +3248,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124841439</v>
+        <v>124835707</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91573</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609243</v>
+        <v>609360</v>
       </c>
       <c r="R27" t="n">
-        <v>7017992</v>
+        <v>7018137</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3458,6 +3329,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3474,37 +3360,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124840461</v>
+        <v>124837331</v>
       </c>
       <c r="B28" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3514,10 +3395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609114</v>
+        <v>609236</v>
       </c>
       <c r="R28" t="n">
-        <v>7018022</v>
+        <v>7018288</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3576,16 +3457,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124838913</v>
+        <v>124840461</v>
       </c>
       <c r="B29" t="n">
         <v>91459</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3616,10 +3492,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609144</v>
+        <v>609114</v>
       </c>
       <c r="R29" t="n">
-        <v>7018039</v>
+        <v>7018022</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3678,37 +3554,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124836321</v>
+        <v>124836351</v>
       </c>
       <c r="B30" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3718,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609324</v>
+        <v>609330</v>
       </c>
       <c r="R30" t="n">
-        <v>7018195</v>
+        <v>7018199</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3780,15 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124838979</v>
+        <v>124835740</v>
       </c>
       <c r="B31" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3796,21 +3662,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3820,10 +3686,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609132</v>
+        <v>609356</v>
       </c>
       <c r="R31" t="n">
-        <v>7018018</v>
+        <v>7018141</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3887,11 +3753,6 @@
       <c r="B32" t="n">
         <v>91131</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>LC</t>
@@ -3984,37 +3845,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124839525</v>
+        <v>124838979</v>
       </c>
       <c r="B33" t="n">
-        <v>91833</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4024,10 +3880,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609068</v>
+        <v>609132</v>
       </c>
       <c r="R33" t="n">
-        <v>7018108</v>
+        <v>7018018</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4086,50 +3942,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124839318</v>
+        <v>124840385</v>
       </c>
       <c r="B34" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västerås, Västerås, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609091</v>
+        <v>609100</v>
       </c>
       <c r="R34" t="n">
-        <v>7018078</v>
+        <v>7018053</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4188,15 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124837411</v>
+        <v>124837223</v>
       </c>
       <c r="B35" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4204,21 +4054,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4078,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>609251</v>
+        <v>609229</v>
       </c>
       <c r="R35" t="n">
-        <v>7018311</v>
+        <v>7018310</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4290,37 +4140,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124837340</v>
+        <v>124836321</v>
       </c>
       <c r="B36" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4175,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>609241</v>
+        <v>609324</v>
       </c>
       <c r="R36" t="n">
-        <v>7018298</v>
+        <v>7018195</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4392,16 +4237,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124839307</v>
+        <v>124837151</v>
       </c>
       <c r="B37" t="n">
         <v>91459</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4432,10 +4272,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>609077</v>
+        <v>609253</v>
       </c>
       <c r="R37" t="n">
-        <v>7018074</v>
+        <v>7018298</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4494,37 +4334,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124836811</v>
+        <v>124837411</v>
       </c>
       <c r="B38" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4534,10 +4369,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>609241</v>
+        <v>609251</v>
       </c>
       <c r="R38" t="n">
-        <v>7018250</v>
+        <v>7018311</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4596,16 +4431,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124839286</v>
+        <v>124838913</v>
       </c>
       <c r="B39" t="n">
         <v>91459</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4636,10 +4466,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>609042</v>
+        <v>609144</v>
       </c>
       <c r="R39" t="n">
-        <v>7018085</v>
+        <v>7018039</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4526,6 +4526,685 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126093534</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>658</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>609380</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7018127</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126094382</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>609259</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7018237</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126095181</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>658</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>609404</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7018211</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126094010</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>658</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>609280</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7018192</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126095076</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>609336</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7018236</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126094104</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>609289</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7018231</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126094201</v>
+      </c>
+      <c r="B46" t="n">
+        <v>103396</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Västerås, Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>609289</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7018253</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -4531,7 +4531,7 @@
         <v>126093534</v>
       </c>
       <c r="B40" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>126094382</v>
       </c>
       <c r="B41" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>126095181</v>
       </c>
       <c r="B42" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>126094010</v>
       </c>
       <c r="B43" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>126095076</v>
       </c>
       <c r="B44" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>126094104</v>
       </c>
       <c r="B45" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>126094201</v>
       </c>
       <c r="B46" t="n">
-        <v>103396</v>
+        <v>103398</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -4531,7 +4531,7 @@
         <v>126093534</v>
       </c>
       <c r="B40" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>126094382</v>
       </c>
       <c r="B41" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>126095181</v>
       </c>
       <c r="B42" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>126094010</v>
       </c>
       <c r="B43" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>126095076</v>
       </c>
       <c r="B44" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>126094104</v>
       </c>
       <c r="B45" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>126094201</v>
       </c>
       <c r="B46" t="n">
-        <v>103398</v>
+        <v>103400</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -4531,7 +4531,7 @@
         <v>126093534</v>
       </c>
       <c r="B40" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>126094382</v>
       </c>
       <c r="B41" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>126095181</v>
       </c>
       <c r="B42" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>126094010</v>
       </c>
       <c r="B43" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>126095076</v>
       </c>
       <c r="B44" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>126094104</v>
       </c>
       <c r="B45" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>126094201</v>
       </c>
       <c r="B46" t="n">
-        <v>103400</v>
+        <v>103404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -4531,7 +4531,7 @@
         <v>126093534</v>
       </c>
       <c r="B40" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>126094382</v>
       </c>
       <c r="B41" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>126095181</v>
       </c>
       <c r="B42" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>126094010</v>
       </c>
       <c r="B43" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>126095076</v>
       </c>
       <c r="B44" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>126094104</v>
       </c>
       <c r="B45" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>126094201</v>
       </c>
       <c r="B46" t="n">
-        <v>103404</v>
+        <v>103417</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -4919,7 +4919,7 @@
         <v>126095076</v>
       </c>
       <c r="B44" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>126094201</v>
       </c>
       <c r="B46" t="n">
-        <v>103417</v>
+        <v>103420</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -4531,7 +4531,7 @@
         <v>126093534</v>
       </c>
       <c r="B40" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>126094382</v>
       </c>
       <c r="B41" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>126095181</v>
       </c>
       <c r="B42" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>126094010</v>
       </c>
       <c r="B43" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>126095076</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>126094104</v>
       </c>
       <c r="B45" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>126094201</v>
       </c>
       <c r="B46" t="n">
-        <v>103420</v>
+        <v>103429</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5210,7 +5210,7 @@
         <v>127025181</v>
       </c>
       <c r="B47" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,37 +5318,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127025192</v>
+        <v>127025174</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609227</v>
+        <v>609192</v>
       </c>
       <c r="R48" t="n">
-        <v>7018351</v>
+        <v>7017983</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5432,7 +5432,7 @@
         <v>127025190</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025195</v>
+        <v>127025192</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609258</v>
+        <v>609227</v>
       </c>
       <c r="R50" t="n">
-        <v>7018359</v>
+        <v>7018351</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5651,37 +5651,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025174</v>
+        <v>127025195</v>
       </c>
       <c r="B51" t="n">
-        <v>91245</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609192</v>
+        <v>609258</v>
       </c>
       <c r="R51" t="n">
-        <v>7017983</v>
+        <v>7018359</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5765,7 +5765,7 @@
         <v>127025182</v>
       </c>
       <c r="B52" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>127025177</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>127025173</v>
       </c>
       <c r="B54" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>127025207</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6216,37 +6216,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127025178</v>
+        <v>127025171</v>
       </c>
       <c r="B56" t="n">
-        <v>98361</v>
+        <v>91615</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609220</v>
+        <v>609272</v>
       </c>
       <c r="R56" t="n">
-        <v>7017949</v>
+        <v>7017889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6327,37 +6327,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127025171</v>
+        <v>127025178</v>
       </c>
       <c r="B57" t="n">
-        <v>91541</v>
+        <v>98436</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609272</v>
+        <v>609220</v>
       </c>
       <c r="R57" t="n">
-        <v>7017889</v>
+        <v>7017949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6441,7 +6441,7 @@
         <v>127025179</v>
       </c>
       <c r="B58" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>127025180</v>
       </c>
       <c r="B59" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6665,37 +6665,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127025189</v>
+        <v>127025202</v>
       </c>
       <c r="B60" t="n">
-        <v>91541</v>
+        <v>98436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>608973</v>
+        <v>609371</v>
       </c>
       <c r="R60" t="n">
-        <v>7018142</v>
+        <v>7018191</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6776,37 +6776,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127025202</v>
+        <v>127025194</v>
       </c>
       <c r="B61" t="n">
-        <v>98361</v>
+        <v>91615</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609371</v>
+        <v>609259</v>
       </c>
       <c r="R61" t="n">
-        <v>7018191</v>
+        <v>7018368</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6887,10 +6887,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127025194</v>
+        <v>127025189</v>
       </c>
       <c r="B62" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609259</v>
+        <v>608973</v>
       </c>
       <c r="R62" t="n">
-        <v>7018368</v>
+        <v>7018142</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7001,7 +7001,7 @@
         <v>127025186</v>
       </c>
       <c r="B63" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7109,37 +7109,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127025185</v>
+        <v>127025172</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>91615</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7148,13 +7148,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609116</v>
+        <v>609245</v>
       </c>
       <c r="R64" t="n">
-        <v>7018095</v>
+        <v>7017919</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7220,37 +7220,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127025172</v>
+        <v>127025199</v>
       </c>
       <c r="B65" t="n">
-        <v>91541</v>
+        <v>98436</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609245</v>
+        <v>609355</v>
       </c>
       <c r="R65" t="n">
-        <v>7017919</v>
+        <v>7018236</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7331,10 +7331,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127025199</v>
+        <v>127025185</v>
       </c>
       <c r="B66" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7370,13 +7370,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609355</v>
+        <v>609116</v>
       </c>
       <c r="R66" t="n">
-        <v>7018236</v>
+        <v>7018095</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7442,37 +7442,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127025175</v>
+        <v>127025191</v>
       </c>
       <c r="B67" t="n">
-        <v>91541</v>
+        <v>98436</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>609186</v>
+        <v>609234</v>
       </c>
       <c r="R67" t="n">
-        <v>7017976</v>
+        <v>7018332</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,37 +7553,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127025191</v>
+        <v>127025175</v>
       </c>
       <c r="B68" t="n">
-        <v>98361</v>
+        <v>91615</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7592,13 +7592,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609234</v>
+        <v>609186</v>
       </c>
       <c r="R68" t="n">
-        <v>7018332</v>
+        <v>7017976</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7664,37 +7664,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127025198</v>
+        <v>127025184</v>
       </c>
       <c r="B69" t="n">
-        <v>98361</v>
+        <v>91615</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609133</v>
+        <v>609141</v>
       </c>
       <c r="R69" t="n">
-        <v>7018247</v>
+        <v>7018041</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7778,7 +7778,7 @@
         <v>127025196</v>
       </c>
       <c r="B70" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7886,37 +7886,37 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127025184</v>
+        <v>127025205</v>
       </c>
       <c r="B71" t="n">
-        <v>91541</v>
+        <v>98436</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7925,13 +7925,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609141</v>
+        <v>609288</v>
       </c>
       <c r="R71" t="n">
-        <v>7018041</v>
+        <v>7018188</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7997,10 +7997,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127025205</v>
+        <v>127025198</v>
       </c>
       <c r="B72" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8036,13 +8036,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609288</v>
+        <v>609133</v>
       </c>
       <c r="R72" t="n">
-        <v>7018188</v>
+        <v>7018247</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8111,7 +8111,7 @@
         <v>127025183</v>
       </c>
       <c r="B73" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>127025188</v>
       </c>
       <c r="B74" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127025206</v>
+        <v>127025197</v>
       </c>
       <c r="B75" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8369,13 +8369,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>609314</v>
+        <v>609193</v>
       </c>
       <c r="R75" t="n">
-        <v>7018167</v>
+        <v>7018250</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8414,12 +8414,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt med plantor inom en cirkel ca 5 m i diameter</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8446,10 +8441,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127025197</v>
+        <v>127025206</v>
       </c>
       <c r="B76" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8476,7 +8471,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8485,13 +8480,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>609193</v>
+        <v>609314</v>
       </c>
       <c r="R76" t="n">
-        <v>7018250</v>
+        <v>7018167</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8520,7 +8515,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8530,7 +8525,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt med plantor inom en cirkel ca 5 m i diameter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8560,7 +8560,7 @@
         <v>127025204</v>
       </c>
       <c r="B77" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>127025203</v>
       </c>
       <c r="B78" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>127025187</v>
       </c>
       <c r="B79" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>127025201</v>
       </c>
       <c r="B80" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5210,7 +5210,7 @@
         <v>127025181</v>
       </c>
       <c r="B47" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5318,37 +5318,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127025174</v>
+        <v>127025190</v>
       </c>
       <c r="B48" t="n">
-        <v>91319</v>
+        <v>98442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609192</v>
+        <v>609164</v>
       </c>
       <c r="R48" t="n">
-        <v>7017983</v>
+        <v>7018293</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5429,10 +5429,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025190</v>
+        <v>127025192</v>
       </c>
       <c r="B49" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609164</v>
+        <v>609227</v>
       </c>
       <c r="R49" t="n">
-        <v>7018293</v>
+        <v>7018351</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025192</v>
+        <v>127025195</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609227</v>
+        <v>609258</v>
       </c>
       <c r="R50" t="n">
-        <v>7018351</v>
+        <v>7018359</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5651,37 +5651,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025195</v>
+        <v>127025174</v>
       </c>
       <c r="B51" t="n">
-        <v>98436</v>
+        <v>91325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609258</v>
+        <v>609192</v>
       </c>
       <c r="R51" t="n">
-        <v>7018359</v>
+        <v>7017983</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5765,7 +5765,7 @@
         <v>127025182</v>
       </c>
       <c r="B52" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>127025177</v>
       </c>
       <c r="B53" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>127025173</v>
       </c>
       <c r="B54" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>127025207</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6216,37 +6216,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127025171</v>
+        <v>127025178</v>
       </c>
       <c r="B56" t="n">
-        <v>91615</v>
+        <v>98442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609272</v>
+        <v>609220</v>
       </c>
       <c r="R56" t="n">
-        <v>7017889</v>
+        <v>7017949</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6327,37 +6327,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127025178</v>
+        <v>127025171</v>
       </c>
       <c r="B57" t="n">
-        <v>98436</v>
+        <v>91621</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609220</v>
+        <v>609272</v>
       </c>
       <c r="R57" t="n">
-        <v>7017949</v>
+        <v>7017889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6441,7 +6441,7 @@
         <v>127025179</v>
       </c>
       <c r="B58" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>127025180</v>
       </c>
       <c r="B59" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6665,37 +6665,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127025202</v>
+        <v>127025194</v>
       </c>
       <c r="B60" t="n">
-        <v>98436</v>
+        <v>91621</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609371</v>
+        <v>609259</v>
       </c>
       <c r="R60" t="n">
-        <v>7018191</v>
+        <v>7018368</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6776,10 +6776,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127025194</v>
+        <v>127025189</v>
       </c>
       <c r="B61" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609259</v>
+        <v>608973</v>
       </c>
       <c r="R61" t="n">
-        <v>7018368</v>
+        <v>7018142</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6887,37 +6887,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127025189</v>
+        <v>127025186</v>
       </c>
       <c r="B62" t="n">
-        <v>91615</v>
+        <v>98442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>608973</v>
+        <v>609123</v>
       </c>
       <c r="R62" t="n">
-        <v>7018142</v>
+        <v>7018113</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6998,10 +6998,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127025186</v>
+        <v>127025202</v>
       </c>
       <c r="B63" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609123</v>
+        <v>609371</v>
       </c>
       <c r="R63" t="n">
-        <v>7018113</v>
+        <v>7018191</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7109,37 +7109,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127025172</v>
+        <v>127025199</v>
       </c>
       <c r="B64" t="n">
-        <v>91615</v>
+        <v>98442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609245</v>
+        <v>609355</v>
       </c>
       <c r="R64" t="n">
-        <v>7017919</v>
+        <v>7018236</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7220,10 +7220,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127025199</v>
+        <v>127025185</v>
       </c>
       <c r="B65" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7259,13 +7259,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609355</v>
+        <v>609116</v>
       </c>
       <c r="R65" t="n">
-        <v>7018236</v>
+        <v>7018095</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7331,37 +7331,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127025185</v>
+        <v>127025172</v>
       </c>
       <c r="B66" t="n">
-        <v>98436</v>
+        <v>91621</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7370,13 +7370,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609116</v>
+        <v>609245</v>
       </c>
       <c r="R66" t="n">
-        <v>7018095</v>
+        <v>7017919</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7445,7 +7445,7 @@
         <v>127025191</v>
       </c>
       <c r="B67" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>127025175</v>
       </c>
       <c r="B68" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7664,37 +7664,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127025184</v>
+        <v>127025196</v>
       </c>
       <c r="B69" t="n">
-        <v>91615</v>
+        <v>98442</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609141</v>
+        <v>609253</v>
       </c>
       <c r="R69" t="n">
-        <v>7018041</v>
+        <v>7018329</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7775,37 +7775,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127025196</v>
+        <v>127025184</v>
       </c>
       <c r="B70" t="n">
-        <v>98436</v>
+        <v>91621</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7814,13 +7814,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609253</v>
+        <v>609141</v>
       </c>
       <c r="R70" t="n">
-        <v>7018329</v>
+        <v>7018041</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7889,7 +7889,7 @@
         <v>127025205</v>
       </c>
       <c r="B71" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127025198</v>
       </c>
       <c r="B72" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>127025183</v>
       </c>
       <c r="B73" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>127025188</v>
       </c>
       <c r="B74" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>127025197</v>
       </c>
       <c r="B75" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>127025206</v>
       </c>
       <c r="B76" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>127025204</v>
       </c>
       <c r="B77" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>127025203</v>
       </c>
       <c r="B78" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8779,37 +8779,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127025187</v>
+        <v>127025201</v>
       </c>
       <c r="B79" t="n">
-        <v>91615</v>
+        <v>98442</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609124</v>
+        <v>609353</v>
       </c>
       <c r="R79" t="n">
-        <v>7018107</v>
+        <v>7018253</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127025201</v>
+        <v>127025187</v>
       </c>
       <c r="B80" t="n">
-        <v>98436</v>
+        <v>91621</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609353</v>
+        <v>609124</v>
       </c>
       <c r="R80" t="n">
-        <v>7018253</v>
+        <v>7018107</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8998,6 +8998,410 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127324923</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>609065</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7018038</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127324920</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>609078</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7018063</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127324921</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>609060</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7018055</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127324922</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98442</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Västerås, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>609075</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7018040</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5318,37 +5318,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127025190</v>
+        <v>127025174</v>
       </c>
       <c r="B48" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609164</v>
+        <v>609192</v>
       </c>
       <c r="R48" t="n">
-        <v>7018293</v>
+        <v>7017983</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5429,7 +5429,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025192</v>
+        <v>127025190</v>
       </c>
       <c r="B49" t="n">
         <v>98442</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609227</v>
+        <v>609164</v>
       </c>
       <c r="R49" t="n">
-        <v>7018351</v>
+        <v>7018293</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5540,7 +5540,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025195</v>
+        <v>127025192</v>
       </c>
       <c r="B50" t="n">
         <v>98442</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609258</v>
+        <v>609227</v>
       </c>
       <c r="R50" t="n">
-        <v>7018359</v>
+        <v>7018351</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5651,37 +5651,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025174</v>
+        <v>127025195</v>
       </c>
       <c r="B51" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609192</v>
+        <v>609258</v>
       </c>
       <c r="R51" t="n">
-        <v>7017983</v>
+        <v>7018359</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7109,37 +7109,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127025199</v>
+        <v>127025172</v>
       </c>
       <c r="B64" t="n">
-        <v>98442</v>
+        <v>91621</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609355</v>
+        <v>609245</v>
       </c>
       <c r="R64" t="n">
-        <v>7018236</v>
+        <v>7017919</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7220,7 +7220,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127025185</v>
+        <v>127025199</v>
       </c>
       <c r="B65" t="n">
         <v>98442</v>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7259,13 +7259,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609116</v>
+        <v>609355</v>
       </c>
       <c r="R65" t="n">
-        <v>7018095</v>
+        <v>7018236</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7331,37 +7331,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127025172</v>
+        <v>127025185</v>
       </c>
       <c r="B66" t="n">
-        <v>91621</v>
+        <v>98442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7370,13 +7370,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609245</v>
+        <v>609116</v>
       </c>
       <c r="R66" t="n">
-        <v>7017919</v>
+        <v>7018095</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7664,7 +7664,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127025196</v>
+        <v>127025205</v>
       </c>
       <c r="B69" t="n">
         <v>98442</v>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609253</v>
+        <v>609288</v>
       </c>
       <c r="R69" t="n">
-        <v>7018329</v>
+        <v>7018188</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7886,7 +7886,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127025205</v>
+        <v>127025196</v>
       </c>
       <c r="B71" t="n">
         <v>98442</v>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7925,13 +7925,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609288</v>
+        <v>609253</v>
       </c>
       <c r="R71" t="n">
-        <v>7018188</v>
+        <v>7018329</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8779,37 +8779,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127025201</v>
+        <v>127025187</v>
       </c>
       <c r="B79" t="n">
-        <v>98442</v>
+        <v>91621</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609353</v>
+        <v>609124</v>
       </c>
       <c r="R79" t="n">
-        <v>7018253</v>
+        <v>7018107</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8890,37 +8890,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127025187</v>
+        <v>127025201</v>
       </c>
       <c r="B80" t="n">
-        <v>91621</v>
+        <v>98442</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609124</v>
+        <v>609353</v>
       </c>
       <c r="R80" t="n">
-        <v>7018107</v>
+        <v>7018253</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5994,37 +5994,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127025173</v>
+        <v>127025207</v>
       </c>
       <c r="B54" t="n">
-        <v>91621</v>
+        <v>98442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609168</v>
+        <v>609388</v>
       </c>
       <c r="R54" t="n">
-        <v>7017966</v>
+        <v>7018181</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,37 +6105,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127025207</v>
+        <v>127025173</v>
       </c>
       <c r="B55" t="n">
-        <v>98442</v>
+        <v>91621</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,13 +6144,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609388</v>
+        <v>609168</v>
       </c>
       <c r="R55" t="n">
-        <v>7018181</v>
+        <v>7017966</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7442,37 +7442,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127025191</v>
+        <v>127025175</v>
       </c>
       <c r="B67" t="n">
-        <v>98442</v>
+        <v>91621</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>609234</v>
+        <v>609186</v>
       </c>
       <c r="R67" t="n">
-        <v>7018332</v>
+        <v>7017976</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,37 +7553,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127025175</v>
+        <v>127025191</v>
       </c>
       <c r="B68" t="n">
-        <v>91621</v>
+        <v>98442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7592,13 +7592,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609186</v>
+        <v>609234</v>
       </c>
       <c r="R68" t="n">
-        <v>7017976</v>
+        <v>7018332</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5210,7 +5210,7 @@
         <v>127025181</v>
       </c>
       <c r="B47" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>127025174</v>
       </c>
       <c r="B48" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>127025190</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>127025192</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>127025195</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>127025182</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>127025177</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5994,37 +5994,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127025207</v>
+        <v>127025173</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>91622</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609388</v>
+        <v>609168</v>
       </c>
       <c r="R54" t="n">
-        <v>7018181</v>
+        <v>7017966</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,37 +6105,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127025173</v>
+        <v>127025207</v>
       </c>
       <c r="B55" t="n">
-        <v>91621</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,13 +6144,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609168</v>
+        <v>609388</v>
       </c>
       <c r="R55" t="n">
-        <v>7017966</v>
+        <v>7018181</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6216,37 +6216,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127025178</v>
+        <v>127025171</v>
       </c>
       <c r="B56" t="n">
-        <v>98442</v>
+        <v>91622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609220</v>
+        <v>609272</v>
       </c>
       <c r="R56" t="n">
-        <v>7017949</v>
+        <v>7017889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6327,37 +6327,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127025171</v>
+        <v>127025178</v>
       </c>
       <c r="B57" t="n">
-        <v>91621</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609272</v>
+        <v>609220</v>
       </c>
       <c r="R57" t="n">
-        <v>7017889</v>
+        <v>7017949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6441,7 +6441,7 @@
         <v>127025179</v>
       </c>
       <c r="B58" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>127025180</v>
       </c>
       <c r="B59" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>127025194</v>
       </c>
       <c r="B60" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>127025189</v>
       </c>
       <c r="B61" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>127025186</v>
       </c>
       <c r="B62" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>127025202</v>
       </c>
       <c r="B63" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>127025172</v>
       </c>
       <c r="B64" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>127025199</v>
       </c>
       <c r="B65" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>127025185</v>
       </c>
       <c r="B66" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>127025175</v>
       </c>
       <c r="B67" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>127025191</v>
       </c>
       <c r="B68" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>127025205</v>
       </c>
       <c r="B69" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7775,37 +7775,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127025184</v>
+        <v>127025196</v>
       </c>
       <c r="B70" t="n">
-        <v>91621</v>
+        <v>98443</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7814,13 +7814,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609141</v>
+        <v>609253</v>
       </c>
       <c r="R70" t="n">
-        <v>7018041</v>
+        <v>7018329</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7886,10 +7886,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127025196</v>
+        <v>127025198</v>
       </c>
       <c r="B71" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609253</v>
+        <v>609133</v>
       </c>
       <c r="R71" t="n">
-        <v>7018329</v>
+        <v>7018247</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7997,37 +7997,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127025198</v>
+        <v>127025184</v>
       </c>
       <c r="B72" t="n">
-        <v>98442</v>
+        <v>91622</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8036,13 +8036,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609133</v>
+        <v>609141</v>
       </c>
       <c r="R72" t="n">
-        <v>7018247</v>
+        <v>7018041</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8111,7 +8111,7 @@
         <v>127025183</v>
       </c>
       <c r="B73" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>127025188</v>
       </c>
       <c r="B74" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>127025197</v>
       </c>
       <c r="B75" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>127025206</v>
       </c>
       <c r="B76" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>127025204</v>
       </c>
       <c r="B77" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>127025203</v>
       </c>
       <c r="B78" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>127025187</v>
       </c>
       <c r="B79" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>127025201</v>
       </c>
       <c r="B80" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>127324923</v>
       </c>
       <c r="B81" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>127324920</v>
       </c>
       <c r="B82" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>127324921</v>
       </c>
       <c r="B83" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>127324922</v>
       </c>
       <c r="B84" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -6216,37 +6216,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127025171</v>
+        <v>127025178</v>
       </c>
       <c r="B56" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609272</v>
+        <v>609220</v>
       </c>
       <c r="R56" t="n">
-        <v>7017889</v>
+        <v>7017949</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6327,37 +6327,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127025178</v>
+        <v>127025171</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609220</v>
+        <v>609272</v>
       </c>
       <c r="R57" t="n">
-        <v>7017949</v>
+        <v>7017889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5318,37 +5318,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127025174</v>
+        <v>127025195</v>
       </c>
       <c r="B48" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609192</v>
+        <v>609258</v>
       </c>
       <c r="R48" t="n">
-        <v>7017983</v>
+        <v>7018359</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5429,7 +5429,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025190</v>
+        <v>127025192</v>
       </c>
       <c r="B49" t="n">
         <v>98443</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609164</v>
+        <v>609227</v>
       </c>
       <c r="R49" t="n">
-        <v>7018293</v>
+        <v>7018351</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5540,7 +5540,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025192</v>
+        <v>127025190</v>
       </c>
       <c r="B50" t="n">
         <v>98443</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609227</v>
+        <v>609164</v>
       </c>
       <c r="R50" t="n">
-        <v>7018351</v>
+        <v>7018293</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5651,37 +5651,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025195</v>
+        <v>127025174</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609258</v>
+        <v>609192</v>
       </c>
       <c r="R51" t="n">
-        <v>7018359</v>
+        <v>7017983</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6216,37 +6216,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127025178</v>
+        <v>127025171</v>
       </c>
       <c r="B56" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609220</v>
+        <v>609272</v>
       </c>
       <c r="R56" t="n">
-        <v>7017949</v>
+        <v>7017889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6327,37 +6327,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127025171</v>
+        <v>127025178</v>
       </c>
       <c r="B57" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609272</v>
+        <v>609220</v>
       </c>
       <c r="R57" t="n">
-        <v>7017889</v>
+        <v>7017949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6887,7 +6887,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127025186</v>
+        <v>127025202</v>
       </c>
       <c r="B62" t="n">
         <v>98443</v>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609123</v>
+        <v>609371</v>
       </c>
       <c r="R62" t="n">
-        <v>7018113</v>
+        <v>7018191</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6998,7 +6998,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127025202</v>
+        <v>127025186</v>
       </c>
       <c r="B63" t="n">
         <v>98443</v>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609371</v>
+        <v>609123</v>
       </c>
       <c r="R63" t="n">
-        <v>7018191</v>
+        <v>7018113</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7220,7 +7220,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127025199</v>
+        <v>127025185</v>
       </c>
       <c r="B65" t="n">
         <v>98443</v>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7259,13 +7259,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609355</v>
+        <v>609116</v>
       </c>
       <c r="R65" t="n">
-        <v>7018236</v>
+        <v>7018095</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7331,7 +7331,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127025185</v>
+        <v>127025199</v>
       </c>
       <c r="B66" t="n">
         <v>98443</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7370,13 +7370,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609116</v>
+        <v>609355</v>
       </c>
       <c r="R66" t="n">
-        <v>7018095</v>
+        <v>7018236</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7664,37 +7664,37 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127025205</v>
+        <v>127025184</v>
       </c>
       <c r="B69" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609288</v>
+        <v>609141</v>
       </c>
       <c r="R69" t="n">
-        <v>7018188</v>
+        <v>7018041</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7775,7 +7775,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127025196</v>
+        <v>127025198</v>
       </c>
       <c r="B70" t="n">
         <v>98443</v>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609253</v>
+        <v>609133</v>
       </c>
       <c r="R70" t="n">
-        <v>7018329</v>
+        <v>7018247</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7886,7 +7886,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127025198</v>
+        <v>127025205</v>
       </c>
       <c r="B71" t="n">
         <v>98443</v>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7925,13 +7925,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609133</v>
+        <v>609288</v>
       </c>
       <c r="R71" t="n">
-        <v>7018247</v>
+        <v>7018188</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7997,37 +7997,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127025184</v>
+        <v>127025196</v>
       </c>
       <c r="B72" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8036,13 +8036,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609141</v>
+        <v>609253</v>
       </c>
       <c r="R72" t="n">
-        <v>7018041</v>
+        <v>7018329</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5994,37 +5994,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127025173</v>
+        <v>127025207</v>
       </c>
       <c r="B54" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609168</v>
+        <v>609388</v>
       </c>
       <c r="R54" t="n">
-        <v>7017966</v>
+        <v>7018181</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,37 +6105,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127025207</v>
+        <v>127025173</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,13 +6144,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609388</v>
+        <v>609168</v>
       </c>
       <c r="R55" t="n">
-        <v>7018181</v>
+        <v>7017966</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5318,37 +5318,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127025195</v>
+        <v>127025174</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609258</v>
+        <v>609192</v>
       </c>
       <c r="R48" t="n">
-        <v>7018359</v>
+        <v>7017983</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5429,7 +5429,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025192</v>
+        <v>127025195</v>
       </c>
       <c r="B49" t="n">
         <v>98443</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609227</v>
+        <v>609258</v>
       </c>
       <c r="R49" t="n">
-        <v>7018351</v>
+        <v>7018359</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5540,7 +5540,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025190</v>
+        <v>127025192</v>
       </c>
       <c r="B50" t="n">
         <v>98443</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609164</v>
+        <v>609227</v>
       </c>
       <c r="R50" t="n">
-        <v>7018293</v>
+        <v>7018351</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5651,37 +5651,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025174</v>
+        <v>127025190</v>
       </c>
       <c r="B51" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609192</v>
+        <v>609164</v>
       </c>
       <c r="R51" t="n">
-        <v>7017983</v>
+        <v>7018293</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5994,37 +5994,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127025207</v>
+        <v>127025173</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>91622</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609388</v>
+        <v>609168</v>
       </c>
       <c r="R54" t="n">
-        <v>7018181</v>
+        <v>7017966</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6105,37 +6105,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127025173</v>
+        <v>127025207</v>
       </c>
       <c r="B55" t="n">
-        <v>91622</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6144,13 +6144,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609168</v>
+        <v>609388</v>
       </c>
       <c r="R55" t="n">
-        <v>7017966</v>
+        <v>7018181</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5210,7 +5210,7 @@
         <v>127025181</v>
       </c>
       <c r="B47" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>127025174</v>
       </c>
       <c r="B48" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5429,10 +5429,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025195</v>
+        <v>127025190</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609258</v>
+        <v>609164</v>
       </c>
       <c r="R49" t="n">
-        <v>7018359</v>
+        <v>7018293</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5543,7 +5543,7 @@
         <v>127025192</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025190</v>
+        <v>127025195</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609164</v>
+        <v>609258</v>
       </c>
       <c r="R51" t="n">
-        <v>7018293</v>
+        <v>7018359</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5765,7 +5765,7 @@
         <v>127025182</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>127025177</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>127025173</v>
       </c>
       <c r="B54" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>127025207</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>127025171</v>
       </c>
       <c r="B56" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>127025178</v>
       </c>
       <c r="B57" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>127025179</v>
       </c>
       <c r="B58" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>127025180</v>
       </c>
       <c r="B59" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>127025194</v>
       </c>
       <c r="B60" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>127025189</v>
       </c>
       <c r="B61" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>127025202</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>127025186</v>
       </c>
       <c r="B63" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7109,37 +7109,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127025172</v>
+        <v>127025199</v>
       </c>
       <c r="B64" t="n">
-        <v>91622</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609245</v>
+        <v>609355</v>
       </c>
       <c r="R64" t="n">
-        <v>7017919</v>
+        <v>7018236</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7223,7 +7223,7 @@
         <v>127025185</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7331,37 +7331,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127025199</v>
+        <v>127025172</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>91626</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609355</v>
+        <v>609245</v>
       </c>
       <c r="R66" t="n">
-        <v>7018236</v>
+        <v>7017919</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7445,7 +7445,7 @@
         <v>127025175</v>
       </c>
       <c r="B67" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>127025191</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>127025184</v>
       </c>
       <c r="B69" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127025198</v>
+        <v>127025205</v>
       </c>
       <c r="B70" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7814,13 +7814,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609133</v>
+        <v>609288</v>
       </c>
       <c r="R70" t="n">
-        <v>7018247</v>
+        <v>7018188</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7886,10 +7886,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127025205</v>
+        <v>127025198</v>
       </c>
       <c r="B71" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7925,13 +7925,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609288</v>
+        <v>609133</v>
       </c>
       <c r="R71" t="n">
-        <v>7018188</v>
+        <v>7018247</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8000,7 +8000,7 @@
         <v>127025196</v>
       </c>
       <c r="B72" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>127025183</v>
       </c>
       <c r="B73" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>127025188</v>
       </c>
       <c r="B74" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>127025197</v>
       </c>
       <c r="B75" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>127025206</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>127025204</v>
       </c>
       <c r="B77" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>127025203</v>
       </c>
       <c r="B78" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>127025187</v>
       </c>
       <c r="B79" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>127025201</v>
       </c>
       <c r="B80" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>127324923</v>
       </c>
       <c r="B81" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>127324920</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>127324921</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>127324922</v>
       </c>
       <c r="B84" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2025 artfynd.xlsx
+++ b/artfynd/A 19224-2025 artfynd.xlsx
@@ -5318,37 +5318,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127025174</v>
+        <v>127025190</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609192</v>
+        <v>609164</v>
       </c>
       <c r="R48" t="n">
-        <v>7017983</v>
+        <v>7018293</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5429,7 +5429,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127025190</v>
+        <v>127025192</v>
       </c>
       <c r="B49" t="n">
         <v>98447</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609164</v>
+        <v>609227</v>
       </c>
       <c r="R49" t="n">
-        <v>7018293</v>
+        <v>7018351</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5540,7 +5540,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127025192</v>
+        <v>127025195</v>
       </c>
       <c r="B50" t="n">
         <v>98447</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609227</v>
+        <v>609258</v>
       </c>
       <c r="R50" t="n">
-        <v>7018351</v>
+        <v>7018359</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5651,37 +5651,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127025195</v>
+        <v>127025174</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609258</v>
+        <v>609192</v>
       </c>
       <c r="R51" t="n">
-        <v>7018359</v>
+        <v>7017983</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6887,7 +6887,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127025202</v>
+        <v>127025186</v>
       </c>
       <c r="B62" t="n">
         <v>98447</v>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609371</v>
+        <v>609123</v>
       </c>
       <c r="R62" t="n">
-        <v>7018191</v>
+        <v>7018113</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6998,7 +6998,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127025186</v>
+        <v>127025202</v>
       </c>
       <c r="B63" t="n">
         <v>98447</v>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609123</v>
+        <v>609371</v>
       </c>
       <c r="R63" t="n">
-        <v>7018113</v>
+        <v>7018191</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7109,37 +7109,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127025199</v>
+        <v>127025172</v>
       </c>
       <c r="B64" t="n">
-        <v>98447</v>
+        <v>91626</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609355</v>
+        <v>609245</v>
       </c>
       <c r="R64" t="n">
-        <v>7018236</v>
+        <v>7017919</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7220,7 +7220,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127025185</v>
+        <v>127025199</v>
       </c>
       <c r="B65" t="n">
         <v>98447</v>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7259,13 +7259,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609116</v>
+        <v>609355</v>
       </c>
       <c r="R65" t="n">
-        <v>7018095</v>
+        <v>7018236</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7331,37 +7331,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127025172</v>
+        <v>127025185</v>
       </c>
       <c r="B66" t="n">
-        <v>91626</v>
+        <v>98447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7370,13 +7370,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609245</v>
+        <v>609116</v>
       </c>
       <c r="R66" t="n">
-        <v>7017919</v>
+        <v>7018095</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,7 +7886,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127025198</v>
+        <v>127025196</v>
       </c>
       <c r="B71" t="n">
         <v>98447</v>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609133</v>
+        <v>609253</v>
       </c>
       <c r="R71" t="n">
-        <v>7018247</v>
+        <v>7018329</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7997,7 +7997,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127025196</v>
+        <v>127025198</v>
       </c>
       <c r="B72" t="n">
         <v>98447</v>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8036,10 +8036,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609253</v>
+        <v>609133</v>
       </c>
       <c r="R72" t="n">
-        <v>7018329</v>
+        <v>7018247</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
